--- a/templates_excel/工种配置.xlsx
+++ b/templates_excel/工种配置.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +49,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,61 +426,2059 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>工种ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>工种名称</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>归属</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>OT001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>数车</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>internal</t>
+          <t>内部</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>OT002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>标印</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>external</t>
+          <t>外部</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n"/>
+      <c r="B46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n"/>
+      <c r="B47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n"/>
+      <c r="B48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n"/>
+      <c r="B49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n"/>
+      <c r="B50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n"/>
+      <c r="B51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n"/>
+      <c r="B52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n"/>
+      <c r="B53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n"/>
+      <c r="B54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n"/>
+      <c r="B55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n"/>
+      <c r="B56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n"/>
+      <c r="B57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n"/>
+      <c r="B58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n"/>
+      <c r="B59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n"/>
+      <c r="B60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n"/>
+      <c r="B61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n"/>
+      <c r="B62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n"/>
+      <c r="B63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n"/>
+      <c r="B64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n"/>
+      <c r="B65" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n"/>
+      <c r="B66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n"/>
+      <c r="B67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n"/>
+      <c r="B68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n"/>
+      <c r="B69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n"/>
+      <c r="B70" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n"/>
+      <c r="B71" s="4" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n"/>
+      <c r="B72" s="4" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n"/>
+      <c r="B73" s="4" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n"/>
+      <c r="B74" s="4" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n"/>
+      <c r="B75" s="4" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n"/>
+      <c r="B76" s="4" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n"/>
+      <c r="B77" s="4" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n"/>
+      <c r="B78" s="4" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n"/>
+      <c r="B79" s="4" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n"/>
+      <c r="B80" s="4" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n"/>
+      <c r="B81" s="4" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n"/>
+      <c r="B82" s="4" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n"/>
+      <c r="B83" s="4" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n"/>
+      <c r="B84" s="4" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n"/>
+      <c r="B85" s="4" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n"/>
+      <c r="B86" s="4" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n"/>
+      <c r="B87" s="4" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n"/>
+      <c r="B88" s="4" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n"/>
+      <c r="B89" s="4" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n"/>
+      <c r="B90" s="4" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="n"/>
+      <c r="B91" s="4" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n"/>
+      <c r="B92" s="4" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n"/>
+      <c r="B93" s="4" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n"/>
+      <c r="B94" s="4" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n"/>
+      <c r="B95" s="4" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n"/>
+      <c r="B96" s="4" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n"/>
+      <c r="B97" s="4" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n"/>
+      <c r="B98" s="4" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n"/>
+      <c r="B99" s="4" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n"/>
+      <c r="B100" s="4" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="n"/>
+      <c r="B101" s="4" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n"/>
+      <c r="B102" s="4" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="n"/>
+      <c r="B103" s="4" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="n"/>
+      <c r="B104" s="4" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="n"/>
+      <c r="B105" s="4" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="n"/>
+      <c r="B106" s="4" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="n"/>
+      <c r="B107" s="4" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="n"/>
+      <c r="B108" s="4" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="n"/>
+      <c r="B109" s="4" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="n"/>
+      <c r="B110" s="4" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n"/>
+      <c r="B111" s="4" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="n"/>
+      <c r="B112" s="4" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="n"/>
+      <c r="B113" s="4" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="n"/>
+      <c r="B114" s="4" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="n"/>
+      <c r="B115" s="4" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="n"/>
+      <c r="B116" s="4" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="n"/>
+      <c r="B117" s="4" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="n"/>
+      <c r="B118" s="4" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="n"/>
+      <c r="B119" s="4" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="n"/>
+      <c r="B120" s="4" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="n"/>
+      <c r="B121" s="4" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="n"/>
+      <c r="B122" s="4" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="n"/>
+      <c r="B123" s="4" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="n"/>
+      <c r="B124" s="4" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="n"/>
+      <c r="B125" s="4" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="n"/>
+      <c r="B126" s="4" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="n"/>
+      <c r="B127" s="4" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="n"/>
+      <c r="B128" s="4" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="n"/>
+      <c r="B129" s="4" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="n"/>
+      <c r="B130" s="4" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="n"/>
+      <c r="B131" s="4" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n"/>
+      <c r="B132" s="4" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="n"/>
+      <c r="B133" s="4" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="n"/>
+      <c r="B134" s="4" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="n"/>
+      <c r="B135" s="4" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="n"/>
+      <c r="B136" s="4" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="n"/>
+      <c r="B137" s="4" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="n"/>
+      <c r="B138" s="4" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="n"/>
+      <c r="B139" s="4" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="n"/>
+      <c r="B140" s="4" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="n"/>
+      <c r="B141" s="4" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="n"/>
+      <c r="B142" s="4" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="n"/>
+      <c r="B143" s="4" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="n"/>
+      <c r="B144" s="4" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="n"/>
+      <c r="B145" s="4" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="n"/>
+      <c r="B146" s="4" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="n"/>
+      <c r="B147" s="4" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="n"/>
+      <c r="B148" s="4" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="n"/>
+      <c r="B149" s="4" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="n"/>
+      <c r="B150" s="4" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="n"/>
+      <c r="B151" s="4" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="n"/>
+      <c r="B152" s="4" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="n"/>
+      <c r="B153" s="4" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="n"/>
+      <c r="B154" s="4" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="n"/>
+      <c r="B155" s="4" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="n"/>
+      <c r="B156" s="4" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="n"/>
+      <c r="B157" s="4" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="n"/>
+      <c r="B158" s="4" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="n"/>
+      <c r="B159" s="4" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="n"/>
+      <c r="B160" s="4" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="n"/>
+      <c r="B161" s="4" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="n"/>
+      <c r="B162" s="4" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="n"/>
+      <c r="B163" s="4" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="n"/>
+      <c r="B164" s="4" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="n"/>
+      <c r="B165" s="4" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="n"/>
+      <c r="B166" s="4" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="n"/>
+      <c r="B167" s="4" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="n"/>
+      <c r="B168" s="4" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="n"/>
+      <c r="B169" s="4" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="n"/>
+      <c r="B170" s="4" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="n"/>
+      <c r="B171" s="4" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="n"/>
+      <c r="B172" s="4" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="n"/>
+      <c r="B173" s="4" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="n"/>
+      <c r="B174" s="4" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="n"/>
+      <c r="B175" s="4" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="n"/>
+      <c r="B176" s="4" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="n"/>
+      <c r="B177" s="4" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="n"/>
+      <c r="B178" s="4" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="n"/>
+      <c r="B179" s="4" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="n"/>
+      <c r="B180" s="4" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="n"/>
+      <c r="B181" s="4" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="n"/>
+      <c r="B182" s="4" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="n"/>
+      <c r="B183" s="4" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="n"/>
+      <c r="B184" s="4" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="n"/>
+      <c r="B185" s="4" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n"/>
+      <c r="B186" s="4" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n"/>
+      <c r="B187" s="4" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n"/>
+      <c r="B188" s="4" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n"/>
+      <c r="B189" s="4" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n"/>
+      <c r="B190" s="4" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n"/>
+      <c r="B191" s="4" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="n"/>
+      <c r="B192" s="4" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="n"/>
+      <c r="B193" s="4" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="n"/>
+      <c r="B194" s="4" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="n"/>
+      <c r="B195" s="4" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="n"/>
+      <c r="B196" s="4" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="n"/>
+      <c r="B197" s="4" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="n"/>
+      <c r="B198" s="4" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="n"/>
+      <c r="B199" s="4" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="n"/>
+      <c r="B200" s="4" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="n"/>
+      <c r="B201" s="4" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="n"/>
+      <c r="B202" s="4" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="n"/>
+      <c r="B203" s="4" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="n"/>
+      <c r="B204" s="4" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="n"/>
+      <c r="B205" s="4" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="n"/>
+      <c r="B206" s="4" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="n"/>
+      <c r="B207" s="4" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="n"/>
+      <c r="B208" s="4" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="n"/>
+      <c r="B209" s="4" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="n"/>
+      <c r="B210" s="4" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="n"/>
+      <c r="B211" s="4" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="n"/>
+      <c r="B212" s="4" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="n"/>
+      <c r="B213" s="4" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="n"/>
+      <c r="B214" s="4" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="n"/>
+      <c r="B215" s="4" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="n"/>
+      <c r="B216" s="4" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="n"/>
+      <c r="B217" s="4" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="n"/>
+      <c r="B218" s="4" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="n"/>
+      <c r="B219" s="4" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="n"/>
+      <c r="B220" s="4" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="n"/>
+      <c r="B221" s="4" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="n"/>
+      <c r="B222" s="4" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="n"/>
+      <c r="B223" s="4" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="n"/>
+      <c r="B224" s="4" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="n"/>
+      <c r="B225" s="4" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="n"/>
+      <c r="B226" s="4" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="n"/>
+      <c r="B227" s="4" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="n"/>
+      <c r="B228" s="4" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="n"/>
+      <c r="B229" s="4" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="n"/>
+      <c r="B230" s="4" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="n"/>
+      <c r="B231" s="4" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="n"/>
+      <c r="B232" s="4" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="n"/>
+      <c r="B233" s="4" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="n"/>
+      <c r="B234" s="4" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="n"/>
+      <c r="B235" s="4" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="n"/>
+      <c r="B236" s="4" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="n"/>
+      <c r="B237" s="4" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="n"/>
+      <c r="B238" s="4" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="n"/>
+      <c r="B239" s="4" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="n"/>
+      <c r="B240" s="4" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="n"/>
+      <c r="B241" s="4" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="n"/>
+      <c r="B242" s="4" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="n"/>
+      <c r="B243" s="4" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="n"/>
+      <c r="B244" s="4" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="4" t="n"/>
+      <c r="B245" s="4" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="n"/>
+      <c r="B246" s="4" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="4" t="n"/>
+      <c r="B247" s="4" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="n"/>
+      <c r="B248" s="4" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="n"/>
+      <c r="B249" s="4" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="n"/>
+      <c r="B250" s="4" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="4" t="n"/>
+      <c r="B251" s="4" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="4" t="n"/>
+      <c r="B252" s="4" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="n"/>
+      <c r="B253" s="4" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="n"/>
+      <c r="B254" s="4" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="n"/>
+      <c r="B255" s="4" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="n"/>
+      <c r="B256" s="4" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="n"/>
+      <c r="B257" s="4" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="n"/>
+      <c r="B258" s="4" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="4" t="n"/>
+      <c r="B259" s="4" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="n"/>
+      <c r="B260" s="4" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="n"/>
+      <c r="B261" s="4" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="4" t="n"/>
+      <c r="B262" s="4" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="n"/>
+      <c r="B263" s="4" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="n"/>
+      <c r="B264" s="4" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="n"/>
+      <c r="B265" s="4" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="n"/>
+      <c r="B266" s="4" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="n"/>
+      <c r="B267" s="4" t="n"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="n"/>
+      <c r="B268" s="4" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="n"/>
+      <c r="B269" s="4" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="n"/>
+      <c r="B270" s="4" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="n"/>
+      <c r="B271" s="4" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="n"/>
+      <c r="B272" s="4" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="n"/>
+      <c r="B273" s="4" t="n"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="n"/>
+      <c r="B274" s="4" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="n"/>
+      <c r="B275" s="4" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="n"/>
+      <c r="B276" s="4" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="4" t="n"/>
+      <c r="B277" s="4" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="4" t="n"/>
+      <c r="B278" s="4" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="n"/>
+      <c r="B279" s="4" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="4" t="n"/>
+      <c r="B280" s="4" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="4" t="n"/>
+      <c r="B281" s="4" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="4" t="n"/>
+      <c r="B282" s="4" t="n"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="4" t="n"/>
+      <c r="B283" s="4" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="4" t="n"/>
+      <c r="B284" s="4" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="4" t="n"/>
+      <c r="B285" s="4" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="4" t="n"/>
+      <c r="B286" s="4" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="4" t="n"/>
+      <c r="B287" s="4" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="4" t="n"/>
+      <c r="B288" s="4" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="4" t="n"/>
+      <c r="B289" s="4" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="4" t="n"/>
+      <c r="B290" s="4" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="4" t="n"/>
+      <c r="B291" s="4" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="4" t="n"/>
+      <c r="B292" s="4" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="4" t="n"/>
+      <c r="B293" s="4" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="4" t="n"/>
+      <c r="B294" s="4" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="4" t="n"/>
+      <c r="B295" s="4" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="4" t="n"/>
+      <c r="B296" s="4" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="4" t="n"/>
+      <c r="B297" s="4" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="4" t="n"/>
+      <c r="B298" s="4" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="4" t="n"/>
+      <c r="B299" s="4" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="4" t="n"/>
+      <c r="B300" s="4" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="4" t="n"/>
+      <c r="B301" s="4" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="4" t="n"/>
+      <c r="B302" s="4" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="n"/>
+      <c r="B303" s="4" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="4" t="n"/>
+      <c r="B304" s="4" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="4" t="n"/>
+      <c r="B305" s="4" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="4" t="n"/>
+      <c r="B306" s="4" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="4" t="n"/>
+      <c r="B307" s="4" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="4" t="n"/>
+      <c r="B308" s="4" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="4" t="n"/>
+      <c r="B309" s="4" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="4" t="n"/>
+      <c r="B310" s="4" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="4" t="n"/>
+      <c r="B311" s="4" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="4" t="n"/>
+      <c r="B312" s="4" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="4" t="n"/>
+      <c r="B313" s="4" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="4" t="n"/>
+      <c r="B314" s="4" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="4" t="n"/>
+      <c r="B315" s="4" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="4" t="n"/>
+      <c r="B316" s="4" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="4" t="n"/>
+      <c r="B317" s="4" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="4" t="n"/>
+      <c r="B318" s="4" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="4" t="n"/>
+      <c r="B319" s="4" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="4" t="n"/>
+      <c r="B320" s="4" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="4" t="n"/>
+      <c r="B321" s="4" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="4" t="n"/>
+      <c r="B322" s="4" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="4" t="n"/>
+      <c r="B323" s="4" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="4" t="n"/>
+      <c r="B324" s="4" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="4" t="n"/>
+      <c r="B325" s="4" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="4" t="n"/>
+      <c r="B326" s="4" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="4" t="n"/>
+      <c r="B327" s="4" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="4" t="n"/>
+      <c r="B328" s="4" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="4" t="n"/>
+      <c r="B329" s="4" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="4" t="n"/>
+      <c r="B330" s="4" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="4" t="n"/>
+      <c r="B331" s="4" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="4" t="n"/>
+      <c r="B332" s="4" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="4" t="n"/>
+      <c r="B333" s="4" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="4" t="n"/>
+      <c r="B334" s="4" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="4" t="n"/>
+      <c r="B335" s="4" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="4" t="n"/>
+      <c r="B336" s="4" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="4" t="n"/>
+      <c r="B337" s="4" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="4" t="n"/>
+      <c r="B338" s="4" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="4" t="n"/>
+      <c r="B339" s="4" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="4" t="n"/>
+      <c r="B340" s="4" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="4" t="n"/>
+      <c r="B341" s="4" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="4" t="n"/>
+      <c r="B342" s="4" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="4" t="n"/>
+      <c r="B343" s="4" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="4" t="n"/>
+      <c r="B344" s="4" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="4" t="n"/>
+      <c r="B345" s="4" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="4" t="n"/>
+      <c r="B346" s="4" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="4" t="n"/>
+      <c r="B347" s="4" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="4" t="n"/>
+      <c r="B348" s="4" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="4" t="n"/>
+      <c r="B349" s="4" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="4" t="n"/>
+      <c r="B350" s="4" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="4" t="n"/>
+      <c r="B351" s="4" t="n"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="4" t="n"/>
+      <c r="B352" s="4" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="4" t="n"/>
+      <c r="B353" s="4" t="n"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="4" t="n"/>
+      <c r="B354" s="4" t="n"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="4" t="n"/>
+      <c r="B355" s="4" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="4" t="n"/>
+      <c r="B356" s="4" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="4" t="n"/>
+      <c r="B357" s="4" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="4" t="n"/>
+      <c r="B358" s="4" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="4" t="n"/>
+      <c r="B359" s="4" t="n"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="4" t="n"/>
+      <c r="B360" s="4" t="n"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="4" t="n"/>
+      <c r="B361" s="4" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="4" t="n"/>
+      <c r="B362" s="4" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="4" t="n"/>
+      <c r="B363" s="4" t="n"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="4" t="n"/>
+      <c r="B364" s="4" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="4" t="n"/>
+      <c r="B365" s="4" t="n"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="4" t="n"/>
+      <c r="B366" s="4" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="4" t="n"/>
+      <c r="B367" s="4" t="n"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="4" t="n"/>
+      <c r="B368" s="4" t="n"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="4" t="n"/>
+      <c r="B369" s="4" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="4" t="n"/>
+      <c r="B370" s="4" t="n"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="4" t="n"/>
+      <c r="B371" s="4" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="4" t="n"/>
+      <c r="B372" s="4" t="n"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="4" t="n"/>
+      <c r="B373" s="4" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="4" t="n"/>
+      <c r="B374" s="4" t="n"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="4" t="n"/>
+      <c r="B375" s="4" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="4" t="n"/>
+      <c r="B376" s="4" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="4" t="n"/>
+      <c r="B377" s="4" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="4" t="n"/>
+      <c r="B378" s="4" t="n"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="4" t="n"/>
+      <c r="B379" s="4" t="n"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="4" t="n"/>
+      <c r="B380" s="4" t="n"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="4" t="n"/>
+      <c r="B381" s="4" t="n"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="4" t="n"/>
+      <c r="B382" s="4" t="n"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="4" t="n"/>
+      <c r="B383" s="4" t="n"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="4" t="n"/>
+      <c r="B384" s="4" t="n"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="4" t="n"/>
+      <c r="B385" s="4" t="n"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="4" t="n"/>
+      <c r="B386" s="4" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="4" t="n"/>
+      <c r="B387" s="4" t="n"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="4" t="n"/>
+      <c r="B388" s="4" t="n"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="4" t="n"/>
+      <c r="B389" s="4" t="n"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="4" t="n"/>
+      <c r="B390" s="4" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="4" t="n"/>
+      <c r="B391" s="4" t="n"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="4" t="n"/>
+      <c r="B392" s="4" t="n"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="4" t="n"/>
+      <c r="B393" s="4" t="n"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="4" t="n"/>
+      <c r="B394" s="4" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="4" t="n"/>
+      <c r="B395" s="4" t="n"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="4" t="n"/>
+      <c r="B396" s="4" t="n"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="4" t="n"/>
+      <c r="B397" s="4" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="4" t="n"/>
+      <c r="B398" s="4" t="n"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="4" t="n"/>
+      <c r="B399" s="4" t="n"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="4" t="n"/>
+      <c r="B400" s="4" t="n"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="4" t="n"/>
+      <c r="B401" s="4" t="n"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="4" t="n"/>
+      <c r="B402" s="4" t="n"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="4" t="n"/>
+      <c r="B403" s="4" t="n"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="4" t="n"/>
+      <c r="B404" s="4" t="n"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="4" t="n"/>
+      <c r="B405" s="4" t="n"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="4" t="n"/>
+      <c r="B406" s="4" t="n"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="4" t="n"/>
+      <c r="B407" s="4" t="n"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="4" t="n"/>
+      <c r="B408" s="4" t="n"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="4" t="n"/>
+      <c r="B409" s="4" t="n"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="4" t="n"/>
+      <c r="B410" s="4" t="n"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="4" t="n"/>
+      <c r="B411" s="4" t="n"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="4" t="n"/>
+      <c r="B412" s="4" t="n"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="4" t="n"/>
+      <c r="B413" s="4" t="n"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="4" t="n"/>
+      <c r="B414" s="4" t="n"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="4" t="n"/>
+      <c r="B415" s="4" t="n"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="4" t="n"/>
+      <c r="B416" s="4" t="n"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="4" t="n"/>
+      <c r="B417" s="4" t="n"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="4" t="n"/>
+      <c r="B418" s="4" t="n"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="4" t="n"/>
+      <c r="B419" s="4" t="n"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="4" t="n"/>
+      <c r="B420" s="4" t="n"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="4" t="n"/>
+      <c r="B421" s="4" t="n"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="4" t="n"/>
+      <c r="B422" s="4" t="n"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="4" t="n"/>
+      <c r="B423" s="4" t="n"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="4" t="n"/>
+      <c r="B424" s="4" t="n"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="4" t="n"/>
+      <c r="B425" s="4" t="n"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="4" t="n"/>
+      <c r="B426" s="4" t="n"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="4" t="n"/>
+      <c r="B427" s="4" t="n"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="4" t="n"/>
+      <c r="B428" s="4" t="n"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="4" t="n"/>
+      <c r="B429" s="4" t="n"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="4" t="n"/>
+      <c r="B430" s="4" t="n"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="4" t="n"/>
+      <c r="B431" s="4" t="n"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="4" t="n"/>
+      <c r="B432" s="4" t="n"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="4" t="n"/>
+      <c r="B433" s="4" t="n"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="4" t="n"/>
+      <c r="B434" s="4" t="n"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="4" t="n"/>
+      <c r="B435" s="4" t="n"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="4" t="n"/>
+      <c r="B436" s="4" t="n"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="4" t="n"/>
+      <c r="B437" s="4" t="n"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="4" t="n"/>
+      <c r="B438" s="4" t="n"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="4" t="n"/>
+      <c r="B439" s="4" t="n"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="4" t="n"/>
+      <c r="B440" s="4" t="n"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="4" t="n"/>
+      <c r="B441" s="4" t="n"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="4" t="n"/>
+      <c r="B442" s="4" t="n"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="4" t="n"/>
+      <c r="B443" s="4" t="n"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="4" t="n"/>
+      <c r="B444" s="4" t="n"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="4" t="n"/>
+      <c r="B445" s="4" t="n"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="4" t="n"/>
+      <c r="B446" s="4" t="n"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="4" t="n"/>
+      <c r="B447" s="4" t="n"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="4" t="n"/>
+      <c r="B448" s="4" t="n"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="4" t="n"/>
+      <c r="B449" s="4" t="n"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="4" t="n"/>
+      <c r="B450" s="4" t="n"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="4" t="n"/>
+      <c r="B451" s="4" t="n"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="4" t="n"/>
+      <c r="B452" s="4" t="n"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="4" t="n"/>
+      <c r="B453" s="4" t="n"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="4" t="n"/>
+      <c r="B454" s="4" t="n"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="4" t="n"/>
+      <c r="B455" s="4" t="n"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="4" t="n"/>
+      <c r="B456" s="4" t="n"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="4" t="n"/>
+      <c r="B457" s="4" t="n"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="4" t="n"/>
+      <c r="B458" s="4" t="n"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="4" t="n"/>
+      <c r="B459" s="4" t="n"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="4" t="n"/>
+      <c r="B460" s="4" t="n"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="4" t="n"/>
+      <c r="B461" s="4" t="n"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="4" t="n"/>
+      <c r="B462" s="4" t="n"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="4" t="n"/>
+      <c r="B463" s="4" t="n"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="4" t="n"/>
+      <c r="B464" s="4" t="n"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="4" t="n"/>
+      <c r="B465" s="4" t="n"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="4" t="n"/>
+      <c r="B466" s="4" t="n"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="4" t="n"/>
+      <c r="B467" s="4" t="n"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="4" t="n"/>
+      <c r="B468" s="4" t="n"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="4" t="n"/>
+      <c r="B469" s="4" t="n"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="4" t="n"/>
+      <c r="B470" s="4" t="n"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="4" t="n"/>
+      <c r="B471" s="4" t="n"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="4" t="n"/>
+      <c r="B472" s="4" t="n"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="4" t="n"/>
+      <c r="B473" s="4" t="n"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="4" t="n"/>
+      <c r="B474" s="4" t="n"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="4" t="n"/>
+      <c r="B475" s="4" t="n"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="4" t="n"/>
+      <c r="B476" s="4" t="n"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="4" t="n"/>
+      <c r="B477" s="4" t="n"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="4" t="n"/>
+      <c r="B478" s="4" t="n"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="4" t="n"/>
+      <c r="B479" s="4" t="n"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="4" t="n"/>
+      <c r="B480" s="4" t="n"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="4" t="n"/>
+      <c r="B481" s="4" t="n"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="4" t="n"/>
+      <c r="B482" s="4" t="n"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="4" t="n"/>
+      <c r="B483" s="4" t="n"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="4" t="n"/>
+      <c r="B484" s="4" t="n"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="4" t="n"/>
+      <c r="B485" s="4" t="n"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="4" t="n"/>
+      <c r="B486" s="4" t="n"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="4" t="n"/>
+      <c r="B487" s="4" t="n"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="4" t="n"/>
+      <c r="B488" s="4" t="n"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="4" t="n"/>
+      <c r="B489" s="4" t="n"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="4" t="n"/>
+      <c r="B490" s="4" t="n"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="4" t="n"/>
+      <c r="B491" s="4" t="n"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="4" t="n"/>
+      <c r="B492" s="4" t="n"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="4" t="n"/>
+      <c r="B493" s="4" t="n"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="4" t="n"/>
+      <c r="B494" s="4" t="n"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="4" t="n"/>
+      <c r="B495" s="4" t="n"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="4" t="n"/>
+      <c r="B496" s="4" t="n"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="4" t="n"/>
+      <c r="B497" s="4" t="n"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="4" t="n"/>
+      <c r="B498" s="4" t="n"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="4" t="n"/>
+      <c r="B499" s="4" t="n"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="4" t="n"/>
+      <c r="B500" s="4" t="n"/>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+      <formula1>"内部,外部"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/templates_excel/工种配置.xlsx
+++ b/templates_excel/工种配置.xlsx
@@ -464,7 +464,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>自制</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>外部</t>
+          <t>外协</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C2:C500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
-      <formula1>"内部,外部"</formula1>
+      <formula1>"自制,外协"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/templates_excel/工种配置.xlsx
+++ b/templates_excel/工种配置.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C500"/>
+  <dimension ref="A1:C699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>工种ID</t>
+          <t>工种编号</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -486,1996 +486,3289 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n"/>
-      <c r="B4" s="4" t="n"/>
+      <c r="A4" s="2" t="n"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="3" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n"/>
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
+      <c r="A6" s="2" t="n"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="4" t="n"/>
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="4" t="n"/>
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="3" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="3" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="3" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="3" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="3" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="4" t="n"/>
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="3" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="4" t="n"/>
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="3" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="n"/>
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="3" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="n"/>
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="3" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="4" t="n"/>
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="3" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="4" t="n"/>
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n"/>
-      <c r="B25" s="4" t="n"/>
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="3" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n"/>
-      <c r="B26" s="4" t="n"/>
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="n"/>
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="3" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="4" t="n"/>
+      <c r="A28" s="2" t="n"/>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="3" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n"/>
-      <c r="B29" s="4" t="n"/>
+      <c r="A29" s="2" t="n"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="3" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n"/>
-      <c r="B30" s="4" t="n"/>
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="3" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n"/>
-      <c r="B31" s="4" t="n"/>
+      <c r="A31" s="2" t="n"/>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n"/>
-      <c r="B32" s="4" t="n"/>
+      <c r="A32" s="2" t="n"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="3" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n"/>
-      <c r="B33" s="4" t="n"/>
+      <c r="A33" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="3" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n"/>
-      <c r="B34" s="4" t="n"/>
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="3" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n"/>
-      <c r="B35" s="4" t="n"/>
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="3" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n"/>
-      <c r="B36" s="4" t="n"/>
+      <c r="A36" s="2" t="n"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="3" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n"/>
-      <c r="B37" s="4" t="n"/>
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="3" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n"/>
-      <c r="B38" s="4" t="n"/>
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n"/>
-      <c r="B39" s="4" t="n"/>
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="3" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n"/>
-      <c r="B40" s="4" t="n"/>
+      <c r="A40" s="2" t="n"/>
+      <c r="B40" s="2" t="n"/>
+      <c r="C40" s="3" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="4" t="n"/>
+      <c r="A41" s="2" t="n"/>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="4" t="n"/>
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="3" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n"/>
-      <c r="B43" s="4" t="n"/>
+      <c r="A43" s="2" t="n"/>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="3" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n"/>
-      <c r="B44" s="4" t="n"/>
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="3" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n"/>
-      <c r="B45" s="4" t="n"/>
+      <c r="A45" s="2" t="n"/>
+      <c r="B45" s="2" t="n"/>
+      <c r="C45" s="3" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n"/>
-      <c r="B46" s="4" t="n"/>
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="3" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n"/>
-      <c r="B47" s="4" t="n"/>
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="3" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n"/>
-      <c r="B48" s="4" t="n"/>
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="3" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n"/>
-      <c r="B49" s="4" t="n"/>
+      <c r="A49" s="2" t="n"/>
+      <c r="B49" s="2" t="n"/>
+      <c r="C49" s="3" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n"/>
-      <c r="B50" s="4" t="n"/>
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="3" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n"/>
-      <c r="B51" s="4" t="n"/>
+      <c r="A51" s="2" t="n"/>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="3" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="n"/>
-      <c r="B52" s="4" t="n"/>
+      <c r="A52" s="2" t="n"/>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="3" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n"/>
-      <c r="B53" s="4" t="n"/>
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="3" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="n"/>
-      <c r="B54" s="4" t="n"/>
+      <c r="A54" s="2" t="n"/>
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="3" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n"/>
-      <c r="B55" s="4" t="n"/>
+      <c r="A55" s="2" t="n"/>
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="3" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="n"/>
-      <c r="B56" s="4" t="n"/>
+      <c r="A56" s="2" t="n"/>
+      <c r="B56" s="2" t="n"/>
+      <c r="C56" s="3" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n"/>
-      <c r="B57" s="4" t="n"/>
+      <c r="A57" s="2" t="n"/>
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="3" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="n"/>
-      <c r="B58" s="4" t="n"/>
+      <c r="A58" s="2" t="n"/>
+      <c r="B58" s="2" t="n"/>
+      <c r="C58" s="3" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n"/>
-      <c r="B59" s="4" t="n"/>
+      <c r="A59" s="2" t="n"/>
+      <c r="B59" s="2" t="n"/>
+      <c r="C59" s="3" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="n"/>
-      <c r="B60" s="4" t="n"/>
+      <c r="A60" s="2" t="n"/>
+      <c r="B60" s="2" t="n"/>
+      <c r="C60" s="3" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n"/>
-      <c r="B61" s="4" t="n"/>
+      <c r="A61" s="2" t="n"/>
+      <c r="B61" s="2" t="n"/>
+      <c r="C61" s="3" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n"/>
-      <c r="B62" s="4" t="n"/>
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="2" t="n"/>
+      <c r="C62" s="3" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n"/>
-      <c r="B63" s="4" t="n"/>
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="3" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="n"/>
-      <c r="B64" s="4" t="n"/>
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="3" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n"/>
-      <c r="B65" s="4" t="n"/>
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="3" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="n"/>
-      <c r="B66" s="4" t="n"/>
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="2" t="n"/>
+      <c r="C66" s="3" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n"/>
-      <c r="B67" s="4" t="n"/>
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="2" t="n"/>
+      <c r="C67" s="3" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="n"/>
-      <c r="B68" s="4" t="n"/>
+      <c r="A68" s="2" t="n"/>
+      <c r="B68" s="2" t="n"/>
+      <c r="C68" s="3" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n"/>
-      <c r="B69" s="4" t="n"/>
+      <c r="A69" s="2" t="n"/>
+      <c r="B69" s="2" t="n"/>
+      <c r="C69" s="3" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="n"/>
-      <c r="B70" s="4" t="n"/>
+      <c r="A70" s="2" t="n"/>
+      <c r="B70" s="2" t="n"/>
+      <c r="C70" s="3" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="n"/>
-      <c r="B71" s="4" t="n"/>
+      <c r="A71" s="2" t="n"/>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="3" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="n"/>
-      <c r="B72" s="4" t="n"/>
+      <c r="A72" s="2" t="n"/>
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="3" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="n"/>
-      <c r="B73" s="4" t="n"/>
+      <c r="A73" s="2" t="n"/>
+      <c r="B73" s="2" t="n"/>
+      <c r="C73" s="3" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="n"/>
-      <c r="B74" s="4" t="n"/>
+      <c r="A74" s="2" t="n"/>
+      <c r="B74" s="2" t="n"/>
+      <c r="C74" s="3" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n"/>
-      <c r="B75" s="4" t="n"/>
+      <c r="A75" s="2" t="n"/>
+      <c r="B75" s="2" t="n"/>
+      <c r="C75" s="3" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="n"/>
-      <c r="B76" s="4" t="n"/>
+      <c r="A76" s="2" t="n"/>
+      <c r="B76" s="2" t="n"/>
+      <c r="C76" s="3" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="n"/>
-      <c r="B77" s="4" t="n"/>
+      <c r="A77" s="2" t="n"/>
+      <c r="B77" s="2" t="n"/>
+      <c r="C77" s="3" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="n"/>
-      <c r="B78" s="4" t="n"/>
+      <c r="A78" s="2" t="n"/>
+      <c r="B78" s="2" t="n"/>
+      <c r="C78" s="3" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="n"/>
-      <c r="B79" s="4" t="n"/>
+      <c r="A79" s="2" t="n"/>
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="3" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="4" t="n"/>
-      <c r="B80" s="4" t="n"/>
+      <c r="A80" s="2" t="n"/>
+      <c r="B80" s="2" t="n"/>
+      <c r="C80" s="3" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="n"/>
-      <c r="B81" s="4" t="n"/>
+      <c r="A81" s="2" t="n"/>
+      <c r="B81" s="2" t="n"/>
+      <c r="C81" s="3" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="n"/>
-      <c r="B82" s="4" t="n"/>
+      <c r="A82" s="2" t="n"/>
+      <c r="B82" s="2" t="n"/>
+      <c r="C82" s="3" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="4" t="n"/>
-      <c r="B83" s="4" t="n"/>
+      <c r="A83" s="2" t="n"/>
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="3" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="n"/>
-      <c r="B84" s="4" t="n"/>
+      <c r="A84" s="2" t="n"/>
+      <c r="B84" s="2" t="n"/>
+      <c r="C84" s="3" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="4" t="n"/>
-      <c r="B85" s="4" t="n"/>
+      <c r="A85" s="2" t="n"/>
+      <c r="B85" s="2" t="n"/>
+      <c r="C85" s="3" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="4" t="n"/>
-      <c r="B86" s="4" t="n"/>
+      <c r="A86" s="2" t="n"/>
+      <c r="B86" s="2" t="n"/>
+      <c r="C86" s="3" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="4" t="n"/>
-      <c r="B87" s="4" t="n"/>
+      <c r="A87" s="2" t="n"/>
+      <c r="B87" s="2" t="n"/>
+      <c r="C87" s="3" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="4" t="n"/>
-      <c r="B88" s="4" t="n"/>
+      <c r="A88" s="2" t="n"/>
+      <c r="B88" s="2" t="n"/>
+      <c r="C88" s="3" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="4" t="n"/>
-      <c r="B89" s="4" t="n"/>
+      <c r="A89" s="2" t="n"/>
+      <c r="B89" s="2" t="n"/>
+      <c r="C89" s="3" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="n"/>
-      <c r="B90" s="4" t="n"/>
+      <c r="A90" s="2" t="n"/>
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="3" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="4" t="n"/>
-      <c r="B91" s="4" t="n"/>
+      <c r="A91" s="2" t="n"/>
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" s="3" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="n"/>
-      <c r="B92" s="4" t="n"/>
+      <c r="A92" s="2" t="n"/>
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" s="3" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="4" t="n"/>
-      <c r="B93" s="4" t="n"/>
+      <c r="A93" s="2" t="n"/>
+      <c r="B93" s="2" t="n"/>
+      <c r="C93" s="3" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="n"/>
-      <c r="B94" s="4" t="n"/>
+      <c r="A94" s="2" t="n"/>
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" s="3" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="n"/>
-      <c r="B95" s="4" t="n"/>
+      <c r="A95" s="2" t="n"/>
+      <c r="B95" s="2" t="n"/>
+      <c r="C95" s="3" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="n"/>
-      <c r="B96" s="4" t="n"/>
+      <c r="A96" s="2" t="n"/>
+      <c r="B96" s="2" t="n"/>
+      <c r="C96" s="3" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="4" t="n"/>
-      <c r="B97" s="4" t="n"/>
+      <c r="A97" s="2" t="n"/>
+      <c r="B97" s="2" t="n"/>
+      <c r="C97" s="3" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="4" t="n"/>
-      <c r="B98" s="4" t="n"/>
+      <c r="A98" s="2" t="n"/>
+      <c r="B98" s="2" t="n"/>
+      <c r="C98" s="3" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="n"/>
-      <c r="B99" s="4" t="n"/>
+      <c r="A99" s="2" t="n"/>
+      <c r="B99" s="2" t="n"/>
+      <c r="C99" s="3" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="4" t="n"/>
-      <c r="B100" s="4" t="n"/>
+      <c r="A100" s="2" t="n"/>
+      <c r="B100" s="2" t="n"/>
+      <c r="C100" s="3" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="4" t="n"/>
-      <c r="B101" s="4" t="n"/>
+      <c r="A101" s="2" t="n"/>
+      <c r="B101" s="2" t="n"/>
+      <c r="C101" s="3" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="4" t="n"/>
-      <c r="B102" s="4" t="n"/>
+      <c r="A102" s="2" t="n"/>
+      <c r="B102" s="2" t="n"/>
+      <c r="C102" s="3" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="n"/>
-      <c r="B103" s="4" t="n"/>
+      <c r="A103" s="2" t="n"/>
+      <c r="B103" s="2" t="n"/>
+      <c r="C103" s="3" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="n"/>
-      <c r="B104" s="4" t="n"/>
+      <c r="A104" s="2" t="n"/>
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" s="3" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="n"/>
-      <c r="B105" s="4" t="n"/>
+      <c r="A105" s="2" t="n"/>
+      <c r="B105" s="2" t="n"/>
+      <c r="C105" s="3" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="4" t="n"/>
-      <c r="B106" s="4" t="n"/>
+      <c r="A106" s="2" t="n"/>
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" s="3" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="4" t="n"/>
-      <c r="B107" s="4" t="n"/>
+      <c r="A107" s="2" t="n"/>
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" s="3" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="4" t="n"/>
-      <c r="B108" s="4" t="n"/>
+      <c r="A108" s="2" t="n"/>
+      <c r="B108" s="2" t="n"/>
+      <c r="C108" s="3" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="4" t="n"/>
-      <c r="B109" s="4" t="n"/>
+      <c r="A109" s="2" t="n"/>
+      <c r="B109" s="2" t="n"/>
+      <c r="C109" s="3" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="n"/>
-      <c r="B110" s="4" t="n"/>
+      <c r="A110" s="2" t="n"/>
+      <c r="B110" s="2" t="n"/>
+      <c r="C110" s="3" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="n"/>
-      <c r="B111" s="4" t="n"/>
+      <c r="A111" s="2" t="n"/>
+      <c r="B111" s="2" t="n"/>
+      <c r="C111" s="3" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="n"/>
-      <c r="B112" s="4" t="n"/>
+      <c r="A112" s="2" t="n"/>
+      <c r="B112" s="2" t="n"/>
+      <c r="C112" s="3" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="4" t="n"/>
-      <c r="B113" s="4" t="n"/>
+      <c r="A113" s="2" t="n"/>
+      <c r="B113" s="2" t="n"/>
+      <c r="C113" s="3" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="n"/>
-      <c r="B114" s="4" t="n"/>
+      <c r="A114" s="2" t="n"/>
+      <c r="B114" s="2" t="n"/>
+      <c r="C114" s="3" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="4" t="n"/>
-      <c r="B115" s="4" t="n"/>
+      <c r="A115" s="2" t="n"/>
+      <c r="B115" s="2" t="n"/>
+      <c r="C115" s="3" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="n"/>
-      <c r="B116" s="4" t="n"/>
+      <c r="A116" s="2" t="n"/>
+      <c r="B116" s="2" t="n"/>
+      <c r="C116" s="3" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="4" t="n"/>
-      <c r="B117" s="4" t="n"/>
+      <c r="A117" s="2" t="n"/>
+      <c r="B117" s="2" t="n"/>
+      <c r="C117" s="3" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="4" t="n"/>
-      <c r="B118" s="4" t="n"/>
+      <c r="A118" s="2" t="n"/>
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="3" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="4" t="n"/>
-      <c r="B119" s="4" t="n"/>
+      <c r="A119" s="2" t="n"/>
+      <c r="B119" s="2" t="n"/>
+      <c r="C119" s="3" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="4" t="n"/>
-      <c r="B120" s="4" t="n"/>
+      <c r="A120" s="2" t="n"/>
+      <c r="B120" s="2" t="n"/>
+      <c r="C120" s="3" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="4" t="n"/>
-      <c r="B121" s="4" t="n"/>
+      <c r="A121" s="2" t="n"/>
+      <c r="B121" s="2" t="n"/>
+      <c r="C121" s="3" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="4" t="n"/>
-      <c r="B122" s="4" t="n"/>
+      <c r="A122" s="2" t="n"/>
+      <c r="B122" s="2" t="n"/>
+      <c r="C122" s="3" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="4" t="n"/>
-      <c r="B123" s="4" t="n"/>
+      <c r="A123" s="2" t="n"/>
+      <c r="B123" s="2" t="n"/>
+      <c r="C123" s="3" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="n"/>
-      <c r="B124" s="4" t="n"/>
+      <c r="A124" s="2" t="n"/>
+      <c r="B124" s="2" t="n"/>
+      <c r="C124" s="3" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="n"/>
-      <c r="B125" s="4" t="n"/>
+      <c r="A125" s="2" t="n"/>
+      <c r="B125" s="2" t="n"/>
+      <c r="C125" s="3" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="4" t="n"/>
-      <c r="B126" s="4" t="n"/>
+      <c r="A126" s="2" t="n"/>
+      <c r="B126" s="2" t="n"/>
+      <c r="C126" s="3" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="4" t="n"/>
-      <c r="B127" s="4" t="n"/>
+      <c r="A127" s="2" t="n"/>
+      <c r="B127" s="2" t="n"/>
+      <c r="C127" s="3" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="4" t="n"/>
-      <c r="B128" s="4" t="n"/>
+      <c r="A128" s="2" t="n"/>
+      <c r="B128" s="2" t="n"/>
+      <c r="C128" s="3" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="4" t="n"/>
-      <c r="B129" s="4" t="n"/>
+      <c r="A129" s="2" t="n"/>
+      <c r="B129" s="2" t="n"/>
+      <c r="C129" s="3" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="4" t="n"/>
-      <c r="B130" s="4" t="n"/>
+      <c r="A130" s="2" t="n"/>
+      <c r="B130" s="2" t="n"/>
+      <c r="C130" s="3" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="4" t="n"/>
-      <c r="B131" s="4" t="n"/>
+      <c r="A131" s="2" t="n"/>
+      <c r="B131" s="2" t="n"/>
+      <c r="C131" s="3" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="4" t="n"/>
-      <c r="B132" s="4" t="n"/>
+      <c r="A132" s="2" t="n"/>
+      <c r="B132" s="2" t="n"/>
+      <c r="C132" s="3" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="4" t="n"/>
-      <c r="B133" s="4" t="n"/>
+      <c r="A133" s="2" t="n"/>
+      <c r="B133" s="2" t="n"/>
+      <c r="C133" s="3" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="4" t="n"/>
-      <c r="B134" s="4" t="n"/>
+      <c r="A134" s="2" t="n"/>
+      <c r="B134" s="2" t="n"/>
+      <c r="C134" s="3" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="4" t="n"/>
-      <c r="B135" s="4" t="n"/>
+      <c r="A135" s="2" t="n"/>
+      <c r="B135" s="2" t="n"/>
+      <c r="C135" s="3" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="4" t="n"/>
-      <c r="B136" s="4" t="n"/>
+      <c r="A136" s="2" t="n"/>
+      <c r="B136" s="2" t="n"/>
+      <c r="C136" s="3" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="4" t="n"/>
-      <c r="B137" s="4" t="n"/>
+      <c r="A137" s="2" t="n"/>
+      <c r="B137" s="2" t="n"/>
+      <c r="C137" s="3" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="4" t="n"/>
-      <c r="B138" s="4" t="n"/>
+      <c r="A138" s="2" t="n"/>
+      <c r="B138" s="2" t="n"/>
+      <c r="C138" s="3" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="4" t="n"/>
-      <c r="B139" s="4" t="n"/>
+      <c r="A139" s="2" t="n"/>
+      <c r="B139" s="2" t="n"/>
+      <c r="C139" s="3" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="4" t="n"/>
-      <c r="B140" s="4" t="n"/>
+      <c r="A140" s="2" t="n"/>
+      <c r="B140" s="2" t="n"/>
+      <c r="C140" s="3" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="4" t="n"/>
-      <c r="B141" s="4" t="n"/>
+      <c r="A141" s="2" t="n"/>
+      <c r="B141" s="2" t="n"/>
+      <c r="C141" s="3" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="4" t="n"/>
-      <c r="B142" s="4" t="n"/>
+      <c r="A142" s="2" t="n"/>
+      <c r="B142" s="2" t="n"/>
+      <c r="C142" s="3" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="4" t="n"/>
-      <c r="B143" s="4" t="n"/>
+      <c r="A143" s="2" t="n"/>
+      <c r="B143" s="2" t="n"/>
+      <c r="C143" s="3" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="4" t="n"/>
-      <c r="B144" s="4" t="n"/>
+      <c r="A144" s="2" t="n"/>
+      <c r="B144" s="2" t="n"/>
+      <c r="C144" s="3" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="4" t="n"/>
-      <c r="B145" s="4" t="n"/>
+      <c r="A145" s="2" t="n"/>
+      <c r="B145" s="2" t="n"/>
+      <c r="C145" s="3" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="4" t="n"/>
-      <c r="B146" s="4" t="n"/>
+      <c r="A146" s="2" t="n"/>
+      <c r="B146" s="2" t="n"/>
+      <c r="C146" s="3" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="4" t="n"/>
-      <c r="B147" s="4" t="n"/>
+      <c r="A147" s="2" t="n"/>
+      <c r="B147" s="2" t="n"/>
+      <c r="C147" s="3" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="4" t="n"/>
-      <c r="B148" s="4" t="n"/>
+      <c r="A148" s="2" t="n"/>
+      <c r="B148" s="2" t="n"/>
+      <c r="C148" s="3" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="4" t="n"/>
-      <c r="B149" s="4" t="n"/>
+      <c r="A149" s="2" t="n"/>
+      <c r="B149" s="2" t="n"/>
+      <c r="C149" s="3" t="n"/>
     </row>
     <row r="150">
-      <c r="A150" s="4" t="n"/>
-      <c r="B150" s="4" t="n"/>
+      <c r="A150" s="2" t="n"/>
+      <c r="B150" s="2" t="n"/>
+      <c r="C150" s="3" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="4" t="n"/>
-      <c r="B151" s="4" t="n"/>
+      <c r="A151" s="2" t="n"/>
+      <c r="B151" s="2" t="n"/>
+      <c r="C151" s="3" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="4" t="n"/>
-      <c r="B152" s="4" t="n"/>
+      <c r="A152" s="2" t="n"/>
+      <c r="B152" s="2" t="n"/>
+      <c r="C152" s="3" t="n"/>
     </row>
     <row r="153">
-      <c r="A153" s="4" t="n"/>
-      <c r="B153" s="4" t="n"/>
+      <c r="A153" s="2" t="n"/>
+      <c r="B153" s="2" t="n"/>
+      <c r="C153" s="3" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="4" t="n"/>
-      <c r="B154" s="4" t="n"/>
+      <c r="A154" s="2" t="n"/>
+      <c r="B154" s="2" t="n"/>
+      <c r="C154" s="3" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="4" t="n"/>
-      <c r="B155" s="4" t="n"/>
+      <c r="A155" s="2" t="n"/>
+      <c r="B155" s="2" t="n"/>
+      <c r="C155" s="3" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="4" t="n"/>
-      <c r="B156" s="4" t="n"/>
+      <c r="A156" s="2" t="n"/>
+      <c r="B156" s="2" t="n"/>
+      <c r="C156" s="3" t="n"/>
     </row>
     <row r="157">
-      <c r="A157" s="4" t="n"/>
-      <c r="B157" s="4" t="n"/>
+      <c r="A157" s="2" t="n"/>
+      <c r="B157" s="2" t="n"/>
+      <c r="C157" s="3" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="4" t="n"/>
-      <c r="B158" s="4" t="n"/>
+      <c r="A158" s="2" t="n"/>
+      <c r="B158" s="2" t="n"/>
+      <c r="C158" s="3" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="4" t="n"/>
-      <c r="B159" s="4" t="n"/>
+      <c r="A159" s="2" t="n"/>
+      <c r="B159" s="2" t="n"/>
+      <c r="C159" s="3" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="4" t="n"/>
-      <c r="B160" s="4" t="n"/>
+      <c r="A160" s="2" t="n"/>
+      <c r="B160" s="2" t="n"/>
+      <c r="C160" s="3" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="4" t="n"/>
-      <c r="B161" s="4" t="n"/>
+      <c r="A161" s="2" t="n"/>
+      <c r="B161" s="2" t="n"/>
+      <c r="C161" s="3" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="4" t="n"/>
-      <c r="B162" s="4" t="n"/>
+      <c r="A162" s="2" t="n"/>
+      <c r="B162" s="2" t="n"/>
+      <c r="C162" s="3" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="4" t="n"/>
-      <c r="B163" s="4" t="n"/>
+      <c r="A163" s="2" t="n"/>
+      <c r="B163" s="2" t="n"/>
+      <c r="C163" s="3" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="4" t="n"/>
-      <c r="B164" s="4" t="n"/>
+      <c r="A164" s="2" t="n"/>
+      <c r="B164" s="2" t="n"/>
+      <c r="C164" s="3" t="n"/>
     </row>
     <row r="165">
-      <c r="A165" s="4" t="n"/>
-      <c r="B165" s="4" t="n"/>
+      <c r="A165" s="2" t="n"/>
+      <c r="B165" s="2" t="n"/>
+      <c r="C165" s="3" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="4" t="n"/>
-      <c r="B166" s="4" t="n"/>
+      <c r="A166" s="2" t="n"/>
+      <c r="B166" s="2" t="n"/>
+      <c r="C166" s="3" t="n"/>
     </row>
     <row r="167">
-      <c r="A167" s="4" t="n"/>
-      <c r="B167" s="4" t="n"/>
+      <c r="A167" s="2" t="n"/>
+      <c r="B167" s="2" t="n"/>
+      <c r="C167" s="3" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="4" t="n"/>
-      <c r="B168" s="4" t="n"/>
+      <c r="A168" s="2" t="n"/>
+      <c r="B168" s="2" t="n"/>
+      <c r="C168" s="3" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="4" t="n"/>
-      <c r="B169" s="4" t="n"/>
+      <c r="A169" s="2" t="n"/>
+      <c r="B169" s="2" t="n"/>
+      <c r="C169" s="3" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="4" t="n"/>
-      <c r="B170" s="4" t="n"/>
+      <c r="A170" s="2" t="n"/>
+      <c r="B170" s="2" t="n"/>
+      <c r="C170" s="3" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="4" t="n"/>
-      <c r="B171" s="4" t="n"/>
+      <c r="A171" s="2" t="n"/>
+      <c r="B171" s="2" t="n"/>
+      <c r="C171" s="3" t="n"/>
     </row>
     <row r="172">
-      <c r="A172" s="4" t="n"/>
-      <c r="B172" s="4" t="n"/>
+      <c r="A172" s="2" t="n"/>
+      <c r="B172" s="2" t="n"/>
+      <c r="C172" s="3" t="n"/>
     </row>
     <row r="173">
-      <c r="A173" s="4" t="n"/>
-      <c r="B173" s="4" t="n"/>
+      <c r="A173" s="2" t="n"/>
+      <c r="B173" s="2" t="n"/>
+      <c r="C173" s="3" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="4" t="n"/>
-      <c r="B174" s="4" t="n"/>
+      <c r="A174" s="2" t="n"/>
+      <c r="B174" s="2" t="n"/>
+      <c r="C174" s="3" t="n"/>
     </row>
     <row r="175">
-      <c r="A175" s="4" t="n"/>
-      <c r="B175" s="4" t="n"/>
+      <c r="A175" s="2" t="n"/>
+      <c r="B175" s="2" t="n"/>
+      <c r="C175" s="3" t="n"/>
     </row>
     <row r="176">
-      <c r="A176" s="4" t="n"/>
-      <c r="B176" s="4" t="n"/>
+      <c r="A176" s="2" t="n"/>
+      <c r="B176" s="2" t="n"/>
+      <c r="C176" s="3" t="n"/>
     </row>
     <row r="177">
-      <c r="A177" s="4" t="n"/>
-      <c r="B177" s="4" t="n"/>
+      <c r="A177" s="2" t="n"/>
+      <c r="B177" s="2" t="n"/>
+      <c r="C177" s="3" t="n"/>
     </row>
     <row r="178">
-      <c r="A178" s="4" t="n"/>
-      <c r="B178" s="4" t="n"/>
+      <c r="A178" s="2" t="n"/>
+      <c r="B178" s="2" t="n"/>
+      <c r="C178" s="3" t="n"/>
     </row>
     <row r="179">
-      <c r="A179" s="4" t="n"/>
-      <c r="B179" s="4" t="n"/>
+      <c r="A179" s="2" t="n"/>
+      <c r="B179" s="2" t="n"/>
+      <c r="C179" s="3" t="n"/>
     </row>
     <row r="180">
-      <c r="A180" s="4" t="n"/>
-      <c r="B180" s="4" t="n"/>
+      <c r="A180" s="2" t="n"/>
+      <c r="B180" s="2" t="n"/>
+      <c r="C180" s="3" t="n"/>
     </row>
     <row r="181">
-      <c r="A181" s="4" t="n"/>
-      <c r="B181" s="4" t="n"/>
+      <c r="A181" s="2" t="n"/>
+      <c r="B181" s="2" t="n"/>
+      <c r="C181" s="3" t="n"/>
     </row>
     <row r="182">
-      <c r="A182" s="4" t="n"/>
-      <c r="B182" s="4" t="n"/>
+      <c r="A182" s="2" t="n"/>
+      <c r="B182" s="2" t="n"/>
+      <c r="C182" s="3" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" s="4" t="n"/>
-      <c r="B183" s="4" t="n"/>
+      <c r="A183" s="2" t="n"/>
+      <c r="B183" s="2" t="n"/>
+      <c r="C183" s="3" t="n"/>
     </row>
     <row r="184">
-      <c r="A184" s="4" t="n"/>
-      <c r="B184" s="4" t="n"/>
+      <c r="A184" s="2" t="n"/>
+      <c r="B184" s="2" t="n"/>
+      <c r="C184" s="3" t="n"/>
     </row>
     <row r="185">
-      <c r="A185" s="4" t="n"/>
-      <c r="B185" s="4" t="n"/>
+      <c r="A185" s="2" t="n"/>
+      <c r="B185" s="2" t="n"/>
+      <c r="C185" s="3" t="n"/>
     </row>
     <row r="186">
-      <c r="A186" s="4" t="n"/>
-      <c r="B186" s="4" t="n"/>
+      <c r="A186" s="2" t="n"/>
+      <c r="B186" s="2" t="n"/>
+      <c r="C186" s="3" t="n"/>
     </row>
     <row r="187">
-      <c r="A187" s="4" t="n"/>
-      <c r="B187" s="4" t="n"/>
+      <c r="A187" s="2" t="n"/>
+      <c r="B187" s="2" t="n"/>
+      <c r="C187" s="3" t="n"/>
     </row>
     <row r="188">
-      <c r="A188" s="4" t="n"/>
-      <c r="B188" s="4" t="n"/>
+      <c r="A188" s="2" t="n"/>
+      <c r="B188" s="2" t="n"/>
+      <c r="C188" s="3" t="n"/>
     </row>
     <row r="189">
-      <c r="A189" s="4" t="n"/>
-      <c r="B189" s="4" t="n"/>
+      <c r="A189" s="2" t="n"/>
+      <c r="B189" s="2" t="n"/>
+      <c r="C189" s="3" t="n"/>
     </row>
     <row r="190">
-      <c r="A190" s="4" t="n"/>
-      <c r="B190" s="4" t="n"/>
+      <c r="A190" s="2" t="n"/>
+      <c r="B190" s="2" t="n"/>
+      <c r="C190" s="3" t="n"/>
     </row>
     <row r="191">
-      <c r="A191" s="4" t="n"/>
-      <c r="B191" s="4" t="n"/>
+      <c r="A191" s="2" t="n"/>
+      <c r="B191" s="2" t="n"/>
+      <c r="C191" s="3" t="n"/>
     </row>
     <row r="192">
-      <c r="A192" s="4" t="n"/>
-      <c r="B192" s="4" t="n"/>
+      <c r="A192" s="2" t="n"/>
+      <c r="B192" s="2" t="n"/>
+      <c r="C192" s="3" t="n"/>
     </row>
     <row r="193">
-      <c r="A193" s="4" t="n"/>
-      <c r="B193" s="4" t="n"/>
+      <c r="A193" s="2" t="n"/>
+      <c r="B193" s="2" t="n"/>
+      <c r="C193" s="3" t="n"/>
     </row>
     <row r="194">
-      <c r="A194" s="4" t="n"/>
-      <c r="B194" s="4" t="n"/>
+      <c r="A194" s="2" t="n"/>
+      <c r="B194" s="2" t="n"/>
+      <c r="C194" s="3" t="n"/>
     </row>
     <row r="195">
-      <c r="A195" s="4" t="n"/>
-      <c r="B195" s="4" t="n"/>
+      <c r="A195" s="2" t="n"/>
+      <c r="B195" s="2" t="n"/>
+      <c r="C195" s="3" t="n"/>
     </row>
     <row r="196">
-      <c r="A196" s="4" t="n"/>
-      <c r="B196" s="4" t="n"/>
+      <c r="A196" s="2" t="n"/>
+      <c r="B196" s="2" t="n"/>
+      <c r="C196" s="3" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" s="4" t="n"/>
-      <c r="B197" s="4" t="n"/>
+      <c r="A197" s="2" t="n"/>
+      <c r="B197" s="2" t="n"/>
+      <c r="C197" s="3" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="4" t="n"/>
-      <c r="B198" s="4" t="n"/>
+      <c r="A198" s="2" t="n"/>
+      <c r="B198" s="2" t="n"/>
+      <c r="C198" s="3" t="n"/>
     </row>
     <row r="199">
-      <c r="A199" s="4" t="n"/>
-      <c r="B199" s="4" t="n"/>
+      <c r="A199" s="2" t="n"/>
+      <c r="B199" s="2" t="n"/>
+      <c r="C199" s="3" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" s="4" t="n"/>
-      <c r="B200" s="4" t="n"/>
+      <c r="A200" s="2" t="n"/>
+      <c r="B200" s="2" t="n"/>
+      <c r="C200" s="3" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="4" t="n"/>
-      <c r="B201" s="4" t="n"/>
+      <c r="A201" s="2" t="n"/>
+      <c r="B201" s="2" t="n"/>
+      <c r="C201" s="3" t="n"/>
     </row>
     <row r="202">
-      <c r="A202" s="4" t="n"/>
-      <c r="B202" s="4" t="n"/>
+      <c r="A202" s="2" t="n"/>
+      <c r="B202" s="2" t="n"/>
+      <c r="C202" s="3" t="n"/>
     </row>
     <row r="203">
-      <c r="A203" s="4" t="n"/>
-      <c r="B203" s="4" t="n"/>
+      <c r="A203" s="2" t="n"/>
+      <c r="B203" s="2" t="n"/>
+      <c r="C203" s="3" t="n"/>
     </row>
     <row r="204">
-      <c r="A204" s="4" t="n"/>
-      <c r="B204" s="4" t="n"/>
+      <c r="A204" s="2" t="n"/>
+      <c r="B204" s="2" t="n"/>
+      <c r="C204" s="3" t="n"/>
     </row>
     <row r="205">
-      <c r="A205" s="4" t="n"/>
-      <c r="B205" s="4" t="n"/>
+      <c r="A205" s="2" t="n"/>
+      <c r="B205" s="2" t="n"/>
+      <c r="C205" s="3" t="n"/>
     </row>
     <row r="206">
-      <c r="A206" s="4" t="n"/>
-      <c r="B206" s="4" t="n"/>
+      <c r="A206" s="2" t="n"/>
+      <c r="B206" s="2" t="n"/>
+      <c r="C206" s="3" t="n"/>
     </row>
     <row r="207">
-      <c r="A207" s="4" t="n"/>
-      <c r="B207" s="4" t="n"/>
+      <c r="A207" s="2" t="n"/>
+      <c r="B207" s="2" t="n"/>
+      <c r="C207" s="3" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="4" t="n"/>
-      <c r="B208" s="4" t="n"/>
+      <c r="A208" s="2" t="n"/>
+      <c r="B208" s="2" t="n"/>
+      <c r="C208" s="3" t="n"/>
     </row>
     <row r="209">
-      <c r="A209" s="4" t="n"/>
-      <c r="B209" s="4" t="n"/>
+      <c r="A209" s="2" t="n"/>
+      <c r="B209" s="2" t="n"/>
+      <c r="C209" s="3" t="n"/>
     </row>
     <row r="210">
-      <c r="A210" s="4" t="n"/>
-      <c r="B210" s="4" t="n"/>
+      <c r="A210" s="2" t="n"/>
+      <c r="B210" s="2" t="n"/>
+      <c r="C210" s="3" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="4" t="n"/>
-      <c r="B211" s="4" t="n"/>
+      <c r="A211" s="2" t="n"/>
+      <c r="B211" s="2" t="n"/>
+      <c r="C211" s="3" t="n"/>
     </row>
     <row r="212">
-      <c r="A212" s="4" t="n"/>
-      <c r="B212" s="4" t="n"/>
+      <c r="A212" s="2" t="n"/>
+      <c r="B212" s="2" t="n"/>
+      <c r="C212" s="3" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="4" t="n"/>
-      <c r="B213" s="4" t="n"/>
+      <c r="A213" s="2" t="n"/>
+      <c r="B213" s="2" t="n"/>
+      <c r="C213" s="3" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="4" t="n"/>
-      <c r="B214" s="4" t="n"/>
+      <c r="A214" s="2" t="n"/>
+      <c r="B214" s="2" t="n"/>
+      <c r="C214" s="3" t="n"/>
     </row>
     <row r="215">
-      <c r="A215" s="4" t="n"/>
-      <c r="B215" s="4" t="n"/>
+      <c r="A215" s="2" t="n"/>
+      <c r="B215" s="2" t="n"/>
+      <c r="C215" s="3" t="n"/>
     </row>
     <row r="216">
-      <c r="A216" s="4" t="n"/>
-      <c r="B216" s="4" t="n"/>
+      <c r="A216" s="2" t="n"/>
+      <c r="B216" s="2" t="n"/>
+      <c r="C216" s="3" t="n"/>
     </row>
     <row r="217">
-      <c r="A217" s="4" t="n"/>
-      <c r="B217" s="4" t="n"/>
+      <c r="A217" s="2" t="n"/>
+      <c r="B217" s="2" t="n"/>
+      <c r="C217" s="3" t="n"/>
     </row>
     <row r="218">
-      <c r="A218" s="4" t="n"/>
-      <c r="B218" s="4" t="n"/>
+      <c r="A218" s="2" t="n"/>
+      <c r="B218" s="2" t="n"/>
+      <c r="C218" s="3" t="n"/>
     </row>
     <row r="219">
-      <c r="A219" s="4" t="n"/>
-      <c r="B219" s="4" t="n"/>
+      <c r="A219" s="2" t="n"/>
+      <c r="B219" s="2" t="n"/>
+      <c r="C219" s="3" t="n"/>
     </row>
     <row r="220">
-      <c r="A220" s="4" t="n"/>
-      <c r="B220" s="4" t="n"/>
+      <c r="A220" s="2" t="n"/>
+      <c r="B220" s="2" t="n"/>
+      <c r="C220" s="3" t="n"/>
     </row>
     <row r="221">
-      <c r="A221" s="4" t="n"/>
-      <c r="B221" s="4" t="n"/>
+      <c r="A221" s="2" t="n"/>
+      <c r="B221" s="2" t="n"/>
+      <c r="C221" s="3" t="n"/>
     </row>
     <row r="222">
-      <c r="A222" s="4" t="n"/>
-      <c r="B222" s="4" t="n"/>
+      <c r="A222" s="2" t="n"/>
+      <c r="B222" s="2" t="n"/>
+      <c r="C222" s="3" t="n"/>
     </row>
     <row r="223">
-      <c r="A223" s="4" t="n"/>
-      <c r="B223" s="4" t="n"/>
+      <c r="A223" s="2" t="n"/>
+      <c r="B223" s="2" t="n"/>
+      <c r="C223" s="3" t="n"/>
     </row>
     <row r="224">
-      <c r="A224" s="4" t="n"/>
-      <c r="B224" s="4" t="n"/>
+      <c r="A224" s="2" t="n"/>
+      <c r="B224" s="2" t="n"/>
+      <c r="C224" s="3" t="n"/>
     </row>
     <row r="225">
-      <c r="A225" s="4" t="n"/>
-      <c r="B225" s="4" t="n"/>
+      <c r="A225" s="2" t="n"/>
+      <c r="B225" s="2" t="n"/>
+      <c r="C225" s="3" t="n"/>
     </row>
     <row r="226">
-      <c r="A226" s="4" t="n"/>
-      <c r="B226" s="4" t="n"/>
+      <c r="A226" s="2" t="n"/>
+      <c r="B226" s="2" t="n"/>
+      <c r="C226" s="3" t="n"/>
     </row>
     <row r="227">
-      <c r="A227" s="4" t="n"/>
-      <c r="B227" s="4" t="n"/>
+      <c r="A227" s="2" t="n"/>
+      <c r="B227" s="2" t="n"/>
+      <c r="C227" s="3" t="n"/>
     </row>
     <row r="228">
-      <c r="A228" s="4" t="n"/>
-      <c r="B228" s="4" t="n"/>
+      <c r="A228" s="2" t="n"/>
+      <c r="B228" s="2" t="n"/>
+      <c r="C228" s="3" t="n"/>
     </row>
     <row r="229">
-      <c r="A229" s="4" t="n"/>
-      <c r="B229" s="4" t="n"/>
+      <c r="A229" s="2" t="n"/>
+      <c r="B229" s="2" t="n"/>
+      <c r="C229" s="3" t="n"/>
     </row>
     <row r="230">
-      <c r="A230" s="4" t="n"/>
-      <c r="B230" s="4" t="n"/>
+      <c r="A230" s="2" t="n"/>
+      <c r="B230" s="2" t="n"/>
+      <c r="C230" s="3" t="n"/>
     </row>
     <row r="231">
-      <c r="A231" s="4" t="n"/>
-      <c r="B231" s="4" t="n"/>
+      <c r="A231" s="2" t="n"/>
+      <c r="B231" s="2" t="n"/>
+      <c r="C231" s="3" t="n"/>
     </row>
     <row r="232">
-      <c r="A232" s="4" t="n"/>
-      <c r="B232" s="4" t="n"/>
+      <c r="A232" s="2" t="n"/>
+      <c r="B232" s="2" t="n"/>
+      <c r="C232" s="3" t="n"/>
     </row>
     <row r="233">
-      <c r="A233" s="4" t="n"/>
-      <c r="B233" s="4" t="n"/>
+      <c r="A233" s="2" t="n"/>
+      <c r="B233" s="2" t="n"/>
+      <c r="C233" s="3" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="4" t="n"/>
-      <c r="B234" s="4" t="n"/>
+      <c r="A234" s="2" t="n"/>
+      <c r="B234" s="2" t="n"/>
+      <c r="C234" s="3" t="n"/>
     </row>
     <row r="235">
-      <c r="A235" s="4" t="n"/>
-      <c r="B235" s="4" t="n"/>
+      <c r="A235" s="2" t="n"/>
+      <c r="B235" s="2" t="n"/>
+      <c r="C235" s="3" t="n"/>
     </row>
     <row r="236">
-      <c r="A236" s="4" t="n"/>
-      <c r="B236" s="4" t="n"/>
+      <c r="A236" s="2" t="n"/>
+      <c r="B236" s="2" t="n"/>
+      <c r="C236" s="3" t="n"/>
     </row>
     <row r="237">
-      <c r="A237" s="4" t="n"/>
-      <c r="B237" s="4" t="n"/>
+      <c r="A237" s="2" t="n"/>
+      <c r="B237" s="2" t="n"/>
+      <c r="C237" s="3" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" s="4" t="n"/>
-      <c r="B238" s="4" t="n"/>
+      <c r="A238" s="2" t="n"/>
+      <c r="B238" s="2" t="n"/>
+      <c r="C238" s="3" t="n"/>
     </row>
     <row r="239">
-      <c r="A239" s="4" t="n"/>
-      <c r="B239" s="4" t="n"/>
+      <c r="A239" s="2" t="n"/>
+      <c r="B239" s="2" t="n"/>
+      <c r="C239" s="3" t="n"/>
     </row>
     <row r="240">
-      <c r="A240" s="4" t="n"/>
-      <c r="B240" s="4" t="n"/>
+      <c r="A240" s="2" t="n"/>
+      <c r="B240" s="2" t="n"/>
+      <c r="C240" s="3" t="n"/>
     </row>
     <row r="241">
-      <c r="A241" s="4" t="n"/>
-      <c r="B241" s="4" t="n"/>
+      <c r="A241" s="2" t="n"/>
+      <c r="B241" s="2" t="n"/>
+      <c r="C241" s="3" t="n"/>
     </row>
     <row r="242">
-      <c r="A242" s="4" t="n"/>
-      <c r="B242" s="4" t="n"/>
+      <c r="A242" s="2" t="n"/>
+      <c r="B242" s="2" t="n"/>
+      <c r="C242" s="3" t="n"/>
     </row>
     <row r="243">
-      <c r="A243" s="4" t="n"/>
-      <c r="B243" s="4" t="n"/>
+      <c r="A243" s="2" t="n"/>
+      <c r="B243" s="2" t="n"/>
+      <c r="C243" s="3" t="n"/>
     </row>
     <row r="244">
-      <c r="A244" s="4" t="n"/>
-      <c r="B244" s="4" t="n"/>
+      <c r="A244" s="2" t="n"/>
+      <c r="B244" s="2" t="n"/>
+      <c r="C244" s="3" t="n"/>
     </row>
     <row r="245">
-      <c r="A245" s="4" t="n"/>
-      <c r="B245" s="4" t="n"/>
+      <c r="A245" s="2" t="n"/>
+      <c r="B245" s="2" t="n"/>
+      <c r="C245" s="3" t="n"/>
     </row>
     <row r="246">
-      <c r="A246" s="4" t="n"/>
-      <c r="B246" s="4" t="n"/>
+      <c r="A246" s="2" t="n"/>
+      <c r="B246" s="2" t="n"/>
+      <c r="C246" s="3" t="n"/>
     </row>
     <row r="247">
-      <c r="A247" s="4" t="n"/>
-      <c r="B247" s="4" t="n"/>
+      <c r="A247" s="2" t="n"/>
+      <c r="B247" s="2" t="n"/>
+      <c r="C247" s="3" t="n"/>
     </row>
     <row r="248">
-      <c r="A248" s="4" t="n"/>
-      <c r="B248" s="4" t="n"/>
+      <c r="A248" s="2" t="n"/>
+      <c r="B248" s="2" t="n"/>
+      <c r="C248" s="3" t="n"/>
     </row>
     <row r="249">
-      <c r="A249" s="4" t="n"/>
-      <c r="B249" s="4" t="n"/>
+      <c r="A249" s="2" t="n"/>
+      <c r="B249" s="2" t="n"/>
+      <c r="C249" s="3" t="n"/>
     </row>
     <row r="250">
-      <c r="A250" s="4" t="n"/>
-      <c r="B250" s="4" t="n"/>
+      <c r="A250" s="2" t="n"/>
+      <c r="B250" s="2" t="n"/>
+      <c r="C250" s="3" t="n"/>
     </row>
     <row r="251">
-      <c r="A251" s="4" t="n"/>
-      <c r="B251" s="4" t="n"/>
+      <c r="A251" s="2" t="n"/>
+      <c r="B251" s="2" t="n"/>
+      <c r="C251" s="3" t="n"/>
     </row>
     <row r="252">
-      <c r="A252" s="4" t="n"/>
-      <c r="B252" s="4" t="n"/>
+      <c r="A252" s="2" t="n"/>
+      <c r="B252" s="2" t="n"/>
+      <c r="C252" s="3" t="n"/>
     </row>
     <row r="253">
-      <c r="A253" s="4" t="n"/>
-      <c r="B253" s="4" t="n"/>
+      <c r="A253" s="2" t="n"/>
+      <c r="B253" s="2" t="n"/>
+      <c r="C253" s="3" t="n"/>
     </row>
     <row r="254">
-      <c r="A254" s="4" t="n"/>
-      <c r="B254" s="4" t="n"/>
+      <c r="A254" s="2" t="n"/>
+      <c r="B254" s="2" t="n"/>
+      <c r="C254" s="3" t="n"/>
     </row>
     <row r="255">
-      <c r="A255" s="4" t="n"/>
-      <c r="B255" s="4" t="n"/>
+      <c r="A255" s="2" t="n"/>
+      <c r="B255" s="2" t="n"/>
+      <c r="C255" s="3" t="n"/>
     </row>
     <row r="256">
-      <c r="A256" s="4" t="n"/>
-      <c r="B256" s="4" t="n"/>
+      <c r="A256" s="2" t="n"/>
+      <c r="B256" s="2" t="n"/>
+      <c r="C256" s="3" t="n"/>
     </row>
     <row r="257">
-      <c r="A257" s="4" t="n"/>
-      <c r="B257" s="4" t="n"/>
+      <c r="A257" s="2" t="n"/>
+      <c r="B257" s="2" t="n"/>
+      <c r="C257" s="3" t="n"/>
     </row>
     <row r="258">
-      <c r="A258" s="4" t="n"/>
-      <c r="B258" s="4" t="n"/>
+      <c r="A258" s="2" t="n"/>
+      <c r="B258" s="2" t="n"/>
+      <c r="C258" s="3" t="n"/>
     </row>
     <row r="259">
-      <c r="A259" s="4" t="n"/>
-      <c r="B259" s="4" t="n"/>
+      <c r="A259" s="2" t="n"/>
+      <c r="B259" s="2" t="n"/>
+      <c r="C259" s="3" t="n"/>
     </row>
     <row r="260">
-      <c r="A260" s="4" t="n"/>
-      <c r="B260" s="4" t="n"/>
+      <c r="A260" s="2" t="n"/>
+      <c r="B260" s="2" t="n"/>
+      <c r="C260" s="3" t="n"/>
     </row>
     <row r="261">
-      <c r="A261" s="4" t="n"/>
-      <c r="B261" s="4" t="n"/>
+      <c r="A261" s="2" t="n"/>
+      <c r="B261" s="2" t="n"/>
+      <c r="C261" s="3" t="n"/>
     </row>
     <row r="262">
-      <c r="A262" s="4" t="n"/>
-      <c r="B262" s="4" t="n"/>
+      <c r="A262" s="2" t="n"/>
+      <c r="B262" s="2" t="n"/>
+      <c r="C262" s="3" t="n"/>
     </row>
     <row r="263">
-      <c r="A263" s="4" t="n"/>
-      <c r="B263" s="4" t="n"/>
+      <c r="A263" s="2" t="n"/>
+      <c r="B263" s="2" t="n"/>
+      <c r="C263" s="3" t="n"/>
     </row>
     <row r="264">
-      <c r="A264" s="4" t="n"/>
-      <c r="B264" s="4" t="n"/>
+      <c r="A264" s="2" t="n"/>
+      <c r="B264" s="2" t="n"/>
+      <c r="C264" s="3" t="n"/>
     </row>
     <row r="265">
-      <c r="A265" s="4" t="n"/>
-      <c r="B265" s="4" t="n"/>
+      <c r="A265" s="2" t="n"/>
+      <c r="B265" s="2" t="n"/>
+      <c r="C265" s="3" t="n"/>
     </row>
     <row r="266">
-      <c r="A266" s="4" t="n"/>
-      <c r="B266" s="4" t="n"/>
+      <c r="A266" s="2" t="n"/>
+      <c r="B266" s="2" t="n"/>
+      <c r="C266" s="3" t="n"/>
     </row>
     <row r="267">
-      <c r="A267" s="4" t="n"/>
-      <c r="B267" s="4" t="n"/>
+      <c r="A267" s="2" t="n"/>
+      <c r="B267" s="2" t="n"/>
+      <c r="C267" s="3" t="n"/>
     </row>
     <row r="268">
-      <c r="A268" s="4" t="n"/>
-      <c r="B268" s="4" t="n"/>
+      <c r="A268" s="2" t="n"/>
+      <c r="B268" s="2" t="n"/>
+      <c r="C268" s="3" t="n"/>
     </row>
     <row r="269">
-      <c r="A269" s="4" t="n"/>
-      <c r="B269" s="4" t="n"/>
+      <c r="A269" s="2" t="n"/>
+      <c r="B269" s="2" t="n"/>
+      <c r="C269" s="3" t="n"/>
     </row>
     <row r="270">
-      <c r="A270" s="4" t="n"/>
-      <c r="B270" s="4" t="n"/>
+      <c r="A270" s="2" t="n"/>
+      <c r="B270" s="2" t="n"/>
+      <c r="C270" s="3" t="n"/>
     </row>
     <row r="271">
-      <c r="A271" s="4" t="n"/>
-      <c r="B271" s="4" t="n"/>
+      <c r="A271" s="2" t="n"/>
+      <c r="B271" s="2" t="n"/>
+      <c r="C271" s="3" t="n"/>
     </row>
     <row r="272">
-      <c r="A272" s="4" t="n"/>
-      <c r="B272" s="4" t="n"/>
+      <c r="A272" s="2" t="n"/>
+      <c r="B272" s="2" t="n"/>
+      <c r="C272" s="3" t="n"/>
     </row>
     <row r="273">
-      <c r="A273" s="4" t="n"/>
-      <c r="B273" s="4" t="n"/>
+      <c r="A273" s="2" t="n"/>
+      <c r="B273" s="2" t="n"/>
+      <c r="C273" s="3" t="n"/>
     </row>
     <row r="274">
-      <c r="A274" s="4" t="n"/>
-      <c r="B274" s="4" t="n"/>
+      <c r="A274" s="2" t="n"/>
+      <c r="B274" s="2" t="n"/>
+      <c r="C274" s="3" t="n"/>
     </row>
     <row r="275">
-      <c r="A275" s="4" t="n"/>
-      <c r="B275" s="4" t="n"/>
+      <c r="A275" s="2" t="n"/>
+      <c r="B275" s="2" t="n"/>
+      <c r="C275" s="3" t="n"/>
     </row>
     <row r="276">
-      <c r="A276" s="4" t="n"/>
-      <c r="B276" s="4" t="n"/>
+      <c r="A276" s="2" t="n"/>
+      <c r="B276" s="2" t="n"/>
+      <c r="C276" s="3" t="n"/>
     </row>
     <row r="277">
-      <c r="A277" s="4" t="n"/>
-      <c r="B277" s="4" t="n"/>
+      <c r="A277" s="2" t="n"/>
+      <c r="B277" s="2" t="n"/>
+      <c r="C277" s="3" t="n"/>
     </row>
     <row r="278">
-      <c r="A278" s="4" t="n"/>
-      <c r="B278" s="4" t="n"/>
+      <c r="A278" s="2" t="n"/>
+      <c r="B278" s="2" t="n"/>
+      <c r="C278" s="3" t="n"/>
     </row>
     <row r="279">
-      <c r="A279" s="4" t="n"/>
-      <c r="B279" s="4" t="n"/>
+      <c r="A279" s="2" t="n"/>
+      <c r="B279" s="2" t="n"/>
+      <c r="C279" s="3" t="n"/>
     </row>
     <row r="280">
-      <c r="A280" s="4" t="n"/>
-      <c r="B280" s="4" t="n"/>
+      <c r="A280" s="2" t="n"/>
+      <c r="B280" s="2" t="n"/>
+      <c r="C280" s="3" t="n"/>
     </row>
     <row r="281">
-      <c r="A281" s="4" t="n"/>
-      <c r="B281" s="4" t="n"/>
+      <c r="A281" s="2" t="n"/>
+      <c r="B281" s="2" t="n"/>
+      <c r="C281" s="3" t="n"/>
     </row>
     <row r="282">
-      <c r="A282" s="4" t="n"/>
-      <c r="B282" s="4" t="n"/>
+      <c r="A282" s="2" t="n"/>
+      <c r="B282" s="2" t="n"/>
+      <c r="C282" s="3" t="n"/>
     </row>
     <row r="283">
-      <c r="A283" s="4" t="n"/>
-      <c r="B283" s="4" t="n"/>
+      <c r="A283" s="2" t="n"/>
+      <c r="B283" s="2" t="n"/>
+      <c r="C283" s="3" t="n"/>
     </row>
     <row r="284">
-      <c r="A284" s="4" t="n"/>
-      <c r="B284" s="4" t="n"/>
+      <c r="A284" s="2" t="n"/>
+      <c r="B284" s="2" t="n"/>
+      <c r="C284" s="3" t="n"/>
     </row>
     <row r="285">
-      <c r="A285" s="4" t="n"/>
-      <c r="B285" s="4" t="n"/>
+      <c r="A285" s="2" t="n"/>
+      <c r="B285" s="2" t="n"/>
+      <c r="C285" s="3" t="n"/>
     </row>
     <row r="286">
-      <c r="A286" s="4" t="n"/>
-      <c r="B286" s="4" t="n"/>
+      <c r="A286" s="2" t="n"/>
+      <c r="B286" s="2" t="n"/>
+      <c r="C286" s="3" t="n"/>
     </row>
     <row r="287">
-      <c r="A287" s="4" t="n"/>
-      <c r="B287" s="4" t="n"/>
+      <c r="A287" s="2" t="n"/>
+      <c r="B287" s="2" t="n"/>
+      <c r="C287" s="3" t="n"/>
     </row>
     <row r="288">
-      <c r="A288" s="4" t="n"/>
-      <c r="B288" s="4" t="n"/>
+      <c r="A288" s="2" t="n"/>
+      <c r="B288" s="2" t="n"/>
+      <c r="C288" s="3" t="n"/>
     </row>
     <row r="289">
-      <c r="A289" s="4" t="n"/>
-      <c r="B289" s="4" t="n"/>
+      <c r="A289" s="2" t="n"/>
+      <c r="B289" s="2" t="n"/>
+      <c r="C289" s="3" t="n"/>
     </row>
     <row r="290">
-      <c r="A290" s="4" t="n"/>
-      <c r="B290" s="4" t="n"/>
+      <c r="A290" s="2" t="n"/>
+      <c r="B290" s="2" t="n"/>
+      <c r="C290" s="3" t="n"/>
     </row>
     <row r="291">
-      <c r="A291" s="4" t="n"/>
-      <c r="B291" s="4" t="n"/>
+      <c r="A291" s="2" t="n"/>
+      <c r="B291" s="2" t="n"/>
+      <c r="C291" s="3" t="n"/>
     </row>
     <row r="292">
-      <c r="A292" s="4" t="n"/>
-      <c r="B292" s="4" t="n"/>
+      <c r="A292" s="2" t="n"/>
+      <c r="B292" s="2" t="n"/>
+      <c r="C292" s="3" t="n"/>
     </row>
     <row r="293">
-      <c r="A293" s="4" t="n"/>
-      <c r="B293" s="4" t="n"/>
+      <c r="A293" s="2" t="n"/>
+      <c r="B293" s="2" t="n"/>
+      <c r="C293" s="3" t="n"/>
     </row>
     <row r="294">
-      <c r="A294" s="4" t="n"/>
-      <c r="B294" s="4" t="n"/>
+      <c r="A294" s="2" t="n"/>
+      <c r="B294" s="2" t="n"/>
+      <c r="C294" s="3" t="n"/>
     </row>
     <row r="295">
-      <c r="A295" s="4" t="n"/>
-      <c r="B295" s="4" t="n"/>
+      <c r="A295" s="2" t="n"/>
+      <c r="B295" s="2" t="n"/>
+      <c r="C295" s="3" t="n"/>
     </row>
     <row r="296">
-      <c r="A296" s="4" t="n"/>
-      <c r="B296" s="4" t="n"/>
+      <c r="A296" s="2" t="n"/>
+      <c r="B296" s="2" t="n"/>
+      <c r="C296" s="3" t="n"/>
     </row>
     <row r="297">
-      <c r="A297" s="4" t="n"/>
-      <c r="B297" s="4" t="n"/>
+      <c r="A297" s="2" t="n"/>
+      <c r="B297" s="2" t="n"/>
+      <c r="C297" s="3" t="n"/>
     </row>
     <row r="298">
-      <c r="A298" s="4" t="n"/>
-      <c r="B298" s="4" t="n"/>
+      <c r="A298" s="2" t="n"/>
+      <c r="B298" s="2" t="n"/>
+      <c r="C298" s="3" t="n"/>
     </row>
     <row r="299">
-      <c r="A299" s="4" t="n"/>
-      <c r="B299" s="4" t="n"/>
+      <c r="A299" s="2" t="n"/>
+      <c r="B299" s="2" t="n"/>
+      <c r="C299" s="3" t="n"/>
     </row>
     <row r="300">
-      <c r="A300" s="4" t="n"/>
-      <c r="B300" s="4" t="n"/>
+      <c r="A300" s="2" t="n"/>
+      <c r="B300" s="2" t="n"/>
+      <c r="C300" s="3" t="n"/>
     </row>
     <row r="301">
-      <c r="A301" s="4" t="n"/>
-      <c r="B301" s="4" t="n"/>
+      <c r="A301" s="2" t="n"/>
+      <c r="B301" s="2" t="n"/>
+      <c r="C301" s="3" t="n"/>
     </row>
     <row r="302">
-      <c r="A302" s="4" t="n"/>
-      <c r="B302" s="4" t="n"/>
+      <c r="A302" s="2" t="n"/>
+      <c r="B302" s="2" t="n"/>
+      <c r="C302" s="3" t="n"/>
     </row>
     <row r="303">
-      <c r="A303" s="4" t="n"/>
-      <c r="B303" s="4" t="n"/>
+      <c r="A303" s="2" t="n"/>
+      <c r="B303" s="2" t="n"/>
+      <c r="C303" s="3" t="n"/>
     </row>
     <row r="304">
-      <c r="A304" s="4" t="n"/>
-      <c r="B304" s="4" t="n"/>
+      <c r="A304" s="2" t="n"/>
+      <c r="B304" s="2" t="n"/>
+      <c r="C304" s="3" t="n"/>
     </row>
     <row r="305">
-      <c r="A305" s="4" t="n"/>
-      <c r="B305" s="4" t="n"/>
+      <c r="A305" s="2" t="n"/>
+      <c r="B305" s="2" t="n"/>
+      <c r="C305" s="3" t="n"/>
     </row>
     <row r="306">
-      <c r="A306" s="4" t="n"/>
-      <c r="B306" s="4" t="n"/>
+      <c r="A306" s="2" t="n"/>
+      <c r="B306" s="2" t="n"/>
+      <c r="C306" s="3" t="n"/>
     </row>
     <row r="307">
-      <c r="A307" s="4" t="n"/>
-      <c r="B307" s="4" t="n"/>
+      <c r="A307" s="2" t="n"/>
+      <c r="B307" s="2" t="n"/>
+      <c r="C307" s="3" t="n"/>
     </row>
     <row r="308">
-      <c r="A308" s="4" t="n"/>
-      <c r="B308" s="4" t="n"/>
+      <c r="A308" s="2" t="n"/>
+      <c r="B308" s="2" t="n"/>
+      <c r="C308" s="3" t="n"/>
     </row>
     <row r="309">
-      <c r="A309" s="4" t="n"/>
-      <c r="B309" s="4" t="n"/>
+      <c r="A309" s="2" t="n"/>
+      <c r="B309" s="2" t="n"/>
+      <c r="C309" s="3" t="n"/>
     </row>
     <row r="310">
-      <c r="A310" s="4" t="n"/>
-      <c r="B310" s="4" t="n"/>
+      <c r="A310" s="2" t="n"/>
+      <c r="B310" s="2" t="n"/>
+      <c r="C310" s="3" t="n"/>
     </row>
     <row r="311">
-      <c r="A311" s="4" t="n"/>
-      <c r="B311" s="4" t="n"/>
+      <c r="A311" s="2" t="n"/>
+      <c r="B311" s="2" t="n"/>
+      <c r="C311" s="3" t="n"/>
     </row>
     <row r="312">
-      <c r="A312" s="4" t="n"/>
-      <c r="B312" s="4" t="n"/>
+      <c r="A312" s="2" t="n"/>
+      <c r="B312" s="2" t="n"/>
+      <c r="C312" s="3" t="n"/>
     </row>
     <row r="313">
-      <c r="A313" s="4" t="n"/>
-      <c r="B313" s="4" t="n"/>
+      <c r="A313" s="2" t="n"/>
+      <c r="B313" s="2" t="n"/>
+      <c r="C313" s="3" t="n"/>
     </row>
     <row r="314">
-      <c r="A314" s="4" t="n"/>
-      <c r="B314" s="4" t="n"/>
+      <c r="A314" s="2" t="n"/>
+      <c r="B314" s="2" t="n"/>
+      <c r="C314" s="3" t="n"/>
     </row>
     <row r="315">
-      <c r="A315" s="4" t="n"/>
-      <c r="B315" s="4" t="n"/>
+      <c r="A315" s="2" t="n"/>
+      <c r="B315" s="2" t="n"/>
+      <c r="C315" s="3" t="n"/>
     </row>
     <row r="316">
-      <c r="A316" s="4" t="n"/>
-      <c r="B316" s="4" t="n"/>
+      <c r="A316" s="2" t="n"/>
+      <c r="B316" s="2" t="n"/>
+      <c r="C316" s="3" t="n"/>
     </row>
     <row r="317">
-      <c r="A317" s="4" t="n"/>
-      <c r="B317" s="4" t="n"/>
+      <c r="A317" s="2" t="n"/>
+      <c r="B317" s="2" t="n"/>
+      <c r="C317" s="3" t="n"/>
     </row>
     <row r="318">
-      <c r="A318" s="4" t="n"/>
-      <c r="B318" s="4" t="n"/>
+      <c r="A318" s="2" t="n"/>
+      <c r="B318" s="2" t="n"/>
+      <c r="C318" s="3" t="n"/>
     </row>
     <row r="319">
-      <c r="A319" s="4" t="n"/>
-      <c r="B319" s="4" t="n"/>
+      <c r="A319" s="2" t="n"/>
+      <c r="B319" s="2" t="n"/>
+      <c r="C319" s="3" t="n"/>
     </row>
     <row r="320">
-      <c r="A320" s="4" t="n"/>
-      <c r="B320" s="4" t="n"/>
+      <c r="A320" s="2" t="n"/>
+      <c r="B320" s="2" t="n"/>
+      <c r="C320" s="3" t="n"/>
     </row>
     <row r="321">
-      <c r="A321" s="4" t="n"/>
-      <c r="B321" s="4" t="n"/>
+      <c r="A321" s="2" t="n"/>
+      <c r="B321" s="2" t="n"/>
+      <c r="C321" s="3" t="n"/>
     </row>
     <row r="322">
-      <c r="A322" s="4" t="n"/>
-      <c r="B322" s="4" t="n"/>
+      <c r="A322" s="2" t="n"/>
+      <c r="B322" s="2" t="n"/>
+      <c r="C322" s="3" t="n"/>
     </row>
     <row r="323">
-      <c r="A323" s="4" t="n"/>
-      <c r="B323" s="4" t="n"/>
+      <c r="A323" s="2" t="n"/>
+      <c r="B323" s="2" t="n"/>
+      <c r="C323" s="3" t="n"/>
     </row>
     <row r="324">
-      <c r="A324" s="4" t="n"/>
-      <c r="B324" s="4" t="n"/>
+      <c r="A324" s="2" t="n"/>
+      <c r="B324" s="2" t="n"/>
+      <c r="C324" s="3" t="n"/>
     </row>
     <row r="325">
-      <c r="A325" s="4" t="n"/>
-      <c r="B325" s="4" t="n"/>
+      <c r="A325" s="2" t="n"/>
+      <c r="B325" s="2" t="n"/>
+      <c r="C325" s="3" t="n"/>
     </row>
     <row r="326">
-      <c r="A326" s="4" t="n"/>
-      <c r="B326" s="4" t="n"/>
+      <c r="A326" s="2" t="n"/>
+      <c r="B326" s="2" t="n"/>
+      <c r="C326" s="3" t="n"/>
     </row>
     <row r="327">
-      <c r="A327" s="4" t="n"/>
-      <c r="B327" s="4" t="n"/>
+      <c r="A327" s="2" t="n"/>
+      <c r="B327" s="2" t="n"/>
+      <c r="C327" s="3" t="n"/>
     </row>
     <row r="328">
-      <c r="A328" s="4" t="n"/>
-      <c r="B328" s="4" t="n"/>
+      <c r="A328" s="2" t="n"/>
+      <c r="B328" s="2" t="n"/>
+      <c r="C328" s="3" t="n"/>
     </row>
     <row r="329">
-      <c r="A329" s="4" t="n"/>
-      <c r="B329" s="4" t="n"/>
+      <c r="A329" s="2" t="n"/>
+      <c r="B329" s="2" t="n"/>
+      <c r="C329" s="3" t="n"/>
     </row>
     <row r="330">
-      <c r="A330" s="4" t="n"/>
-      <c r="B330" s="4" t="n"/>
+      <c r="A330" s="2" t="n"/>
+      <c r="B330" s="2" t="n"/>
+      <c r="C330" s="3" t="n"/>
     </row>
     <row r="331">
-      <c r="A331" s="4" t="n"/>
-      <c r="B331" s="4" t="n"/>
+      <c r="A331" s="2" t="n"/>
+      <c r="B331" s="2" t="n"/>
+      <c r="C331" s="3" t="n"/>
     </row>
     <row r="332">
-      <c r="A332" s="4" t="n"/>
-      <c r="B332" s="4" t="n"/>
+      <c r="A332" s="2" t="n"/>
+      <c r="B332" s="2" t="n"/>
+      <c r="C332" s="3" t="n"/>
     </row>
     <row r="333">
-      <c r="A333" s="4" t="n"/>
-      <c r="B333" s="4" t="n"/>
+      <c r="A333" s="2" t="n"/>
+      <c r="B333" s="2" t="n"/>
+      <c r="C333" s="3" t="n"/>
     </row>
     <row r="334">
-      <c r="A334" s="4" t="n"/>
-      <c r="B334" s="4" t="n"/>
+      <c r="A334" s="2" t="n"/>
+      <c r="B334" s="2" t="n"/>
+      <c r="C334" s="3" t="n"/>
     </row>
     <row r="335">
-      <c r="A335" s="4" t="n"/>
-      <c r="B335" s="4" t="n"/>
+      <c r="A335" s="2" t="n"/>
+      <c r="B335" s="2" t="n"/>
+      <c r="C335" s="3" t="n"/>
     </row>
     <row r="336">
-      <c r="A336" s="4" t="n"/>
-      <c r="B336" s="4" t="n"/>
+      <c r="A336" s="2" t="n"/>
+      <c r="B336" s="2" t="n"/>
+      <c r="C336" s="3" t="n"/>
     </row>
     <row r="337">
-      <c r="A337" s="4" t="n"/>
-      <c r="B337" s="4" t="n"/>
+      <c r="A337" s="2" t="n"/>
+      <c r="B337" s="2" t="n"/>
+      <c r="C337" s="3" t="n"/>
     </row>
     <row r="338">
-      <c r="A338" s="4" t="n"/>
-      <c r="B338" s="4" t="n"/>
+      <c r="A338" s="2" t="n"/>
+      <c r="B338" s="2" t="n"/>
+      <c r="C338" s="3" t="n"/>
     </row>
     <row r="339">
-      <c r="A339" s="4" t="n"/>
-      <c r="B339" s="4" t="n"/>
+      <c r="A339" s="2" t="n"/>
+      <c r="B339" s="2" t="n"/>
+      <c r="C339" s="3" t="n"/>
     </row>
     <row r="340">
-      <c r="A340" s="4" t="n"/>
-      <c r="B340" s="4" t="n"/>
+      <c r="A340" s="2" t="n"/>
+      <c r="B340" s="2" t="n"/>
+      <c r="C340" s="3" t="n"/>
     </row>
     <row r="341">
-      <c r="A341" s="4" t="n"/>
-      <c r="B341" s="4" t="n"/>
+      <c r="A341" s="2" t="n"/>
+      <c r="B341" s="2" t="n"/>
+      <c r="C341" s="3" t="n"/>
     </row>
     <row r="342">
-      <c r="A342" s="4" t="n"/>
-      <c r="B342" s="4" t="n"/>
+      <c r="A342" s="2" t="n"/>
+      <c r="B342" s="2" t="n"/>
+      <c r="C342" s="3" t="n"/>
     </row>
     <row r="343">
-      <c r="A343" s="4" t="n"/>
-      <c r="B343" s="4" t="n"/>
+      <c r="A343" s="2" t="n"/>
+      <c r="B343" s="2" t="n"/>
+      <c r="C343" s="3" t="n"/>
     </row>
     <row r="344">
-      <c r="A344" s="4" t="n"/>
-      <c r="B344" s="4" t="n"/>
+      <c r="A344" s="2" t="n"/>
+      <c r="B344" s="2" t="n"/>
+      <c r="C344" s="3" t="n"/>
     </row>
     <row r="345">
-      <c r="A345" s="4" t="n"/>
-      <c r="B345" s="4" t="n"/>
+      <c r="A345" s="2" t="n"/>
+      <c r="B345" s="2" t="n"/>
+      <c r="C345" s="3" t="n"/>
     </row>
     <row r="346">
-      <c r="A346" s="4" t="n"/>
-      <c r="B346" s="4" t="n"/>
+      <c r="A346" s="2" t="n"/>
+      <c r="B346" s="2" t="n"/>
+      <c r="C346" s="3" t="n"/>
     </row>
     <row r="347">
-      <c r="A347" s="4" t="n"/>
-      <c r="B347" s="4" t="n"/>
+      <c r="A347" s="2" t="n"/>
+      <c r="B347" s="2" t="n"/>
+      <c r="C347" s="3" t="n"/>
     </row>
     <row r="348">
-      <c r="A348" s="4" t="n"/>
-      <c r="B348" s="4" t="n"/>
+      <c r="A348" s="2" t="n"/>
+      <c r="B348" s="2" t="n"/>
+      <c r="C348" s="3" t="n"/>
     </row>
     <row r="349">
-      <c r="A349" s="4" t="n"/>
-      <c r="B349" s="4" t="n"/>
+      <c r="A349" s="2" t="n"/>
+      <c r="B349" s="2" t="n"/>
+      <c r="C349" s="3" t="n"/>
     </row>
     <row r="350">
-      <c r="A350" s="4" t="n"/>
-      <c r="B350" s="4" t="n"/>
+      <c r="A350" s="2" t="n"/>
+      <c r="B350" s="2" t="n"/>
+      <c r="C350" s="3" t="n"/>
     </row>
     <row r="351">
-      <c r="A351" s="4" t="n"/>
-      <c r="B351" s="4" t="n"/>
+      <c r="A351" s="2" t="n"/>
+      <c r="B351" s="2" t="n"/>
+      <c r="C351" s="3" t="n"/>
     </row>
     <row r="352">
-      <c r="A352" s="4" t="n"/>
-      <c r="B352" s="4" t="n"/>
+      <c r="A352" s="2" t="n"/>
+      <c r="B352" s="2" t="n"/>
+      <c r="C352" s="3" t="n"/>
     </row>
     <row r="353">
-      <c r="A353" s="4" t="n"/>
-      <c r="B353" s="4" t="n"/>
+      <c r="A353" s="2" t="n"/>
+      <c r="B353" s="2" t="n"/>
+      <c r="C353" s="3" t="n"/>
     </row>
     <row r="354">
-      <c r="A354" s="4" t="n"/>
-      <c r="B354" s="4" t="n"/>
+      <c r="A354" s="2" t="n"/>
+      <c r="B354" s="2" t="n"/>
+      <c r="C354" s="3" t="n"/>
     </row>
     <row r="355">
-      <c r="A355" s="4" t="n"/>
-      <c r="B355" s="4" t="n"/>
+      <c r="A355" s="2" t="n"/>
+      <c r="B355" s="2" t="n"/>
+      <c r="C355" s="3" t="n"/>
     </row>
     <row r="356">
-      <c r="A356" s="4" t="n"/>
-      <c r="B356" s="4" t="n"/>
+      <c r="A356" s="2" t="n"/>
+      <c r="B356" s="2" t="n"/>
+      <c r="C356" s="3" t="n"/>
     </row>
     <row r="357">
-      <c r="A357" s="4" t="n"/>
-      <c r="B357" s="4" t="n"/>
+      <c r="A357" s="2" t="n"/>
+      <c r="B357" s="2" t="n"/>
+      <c r="C357" s="3" t="n"/>
     </row>
     <row r="358">
-      <c r="A358" s="4" t="n"/>
-      <c r="B358" s="4" t="n"/>
+      <c r="A358" s="2" t="n"/>
+      <c r="B358" s="2" t="n"/>
+      <c r="C358" s="3" t="n"/>
     </row>
     <row r="359">
-      <c r="A359" s="4" t="n"/>
-      <c r="B359" s="4" t="n"/>
+      <c r="A359" s="2" t="n"/>
+      <c r="B359" s="2" t="n"/>
+      <c r="C359" s="3" t="n"/>
     </row>
     <row r="360">
-      <c r="A360" s="4" t="n"/>
-      <c r="B360" s="4" t="n"/>
+      <c r="A360" s="2" t="n"/>
+      <c r="B360" s="2" t="n"/>
+      <c r="C360" s="3" t="n"/>
     </row>
     <row r="361">
-      <c r="A361" s="4" t="n"/>
-      <c r="B361" s="4" t="n"/>
+      <c r="A361" s="2" t="n"/>
+      <c r="B361" s="2" t="n"/>
+      <c r="C361" s="3" t="n"/>
     </row>
     <row r="362">
-      <c r="A362" s="4" t="n"/>
-      <c r="B362" s="4" t="n"/>
+      <c r="A362" s="2" t="n"/>
+      <c r="B362" s="2" t="n"/>
+      <c r="C362" s="3" t="n"/>
     </row>
     <row r="363">
-      <c r="A363" s="4" t="n"/>
-      <c r="B363" s="4" t="n"/>
+      <c r="A363" s="2" t="n"/>
+      <c r="B363" s="2" t="n"/>
+      <c r="C363" s="3" t="n"/>
     </row>
     <row r="364">
-      <c r="A364" s="4" t="n"/>
-      <c r="B364" s="4" t="n"/>
+      <c r="A364" s="2" t="n"/>
+      <c r="B364" s="2" t="n"/>
+      <c r="C364" s="3" t="n"/>
     </row>
     <row r="365">
-      <c r="A365" s="4" t="n"/>
-      <c r="B365" s="4" t="n"/>
+      <c r="A365" s="2" t="n"/>
+      <c r="B365" s="2" t="n"/>
+      <c r="C365" s="3" t="n"/>
     </row>
     <row r="366">
-      <c r="A366" s="4" t="n"/>
-      <c r="B366" s="4" t="n"/>
+      <c r="A366" s="2" t="n"/>
+      <c r="B366" s="2" t="n"/>
+      <c r="C366" s="3" t="n"/>
     </row>
     <row r="367">
-      <c r="A367" s="4" t="n"/>
-      <c r="B367" s="4" t="n"/>
+      <c r="A367" s="2" t="n"/>
+      <c r="B367" s="2" t="n"/>
+      <c r="C367" s="3" t="n"/>
     </row>
     <row r="368">
-      <c r="A368" s="4" t="n"/>
-      <c r="B368" s="4" t="n"/>
+      <c r="A368" s="2" t="n"/>
+      <c r="B368" s="2" t="n"/>
+      <c r="C368" s="3" t="n"/>
     </row>
     <row r="369">
-      <c r="A369" s="4" t="n"/>
-      <c r="B369" s="4" t="n"/>
+      <c r="A369" s="2" t="n"/>
+      <c r="B369" s="2" t="n"/>
+      <c r="C369" s="3" t="n"/>
     </row>
     <row r="370">
-      <c r="A370" s="4" t="n"/>
-      <c r="B370" s="4" t="n"/>
+      <c r="A370" s="2" t="n"/>
+      <c r="B370" s="2" t="n"/>
+      <c r="C370" s="3" t="n"/>
     </row>
     <row r="371">
-      <c r="A371" s="4" t="n"/>
-      <c r="B371" s="4" t="n"/>
+      <c r="A371" s="2" t="n"/>
+      <c r="B371" s="2" t="n"/>
+      <c r="C371" s="3" t="n"/>
     </row>
     <row r="372">
-      <c r="A372" s="4" t="n"/>
-      <c r="B372" s="4" t="n"/>
+      <c r="A372" s="2" t="n"/>
+      <c r="B372" s="2" t="n"/>
+      <c r="C372" s="3" t="n"/>
     </row>
     <row r="373">
-      <c r="A373" s="4" t="n"/>
-      <c r="B373" s="4" t="n"/>
+      <c r="A373" s="2" t="n"/>
+      <c r="B373" s="2" t="n"/>
+      <c r="C373" s="3" t="n"/>
     </row>
     <row r="374">
-      <c r="A374" s="4" t="n"/>
-      <c r="B374" s="4" t="n"/>
+      <c r="A374" s="2" t="n"/>
+      <c r="B374" s="2" t="n"/>
+      <c r="C374" s="3" t="n"/>
     </row>
     <row r="375">
-      <c r="A375" s="4" t="n"/>
-      <c r="B375" s="4" t="n"/>
+      <c r="A375" s="2" t="n"/>
+      <c r="B375" s="2" t="n"/>
+      <c r="C375" s="3" t="n"/>
     </row>
     <row r="376">
-      <c r="A376" s="4" t="n"/>
-      <c r="B376" s="4" t="n"/>
+      <c r="A376" s="2" t="n"/>
+      <c r="B376" s="2" t="n"/>
+      <c r="C376" s="3" t="n"/>
     </row>
     <row r="377">
-      <c r="A377" s="4" t="n"/>
-      <c r="B377" s="4" t="n"/>
+      <c r="A377" s="2" t="n"/>
+      <c r="B377" s="2" t="n"/>
+      <c r="C377" s="3" t="n"/>
     </row>
     <row r="378">
-      <c r="A378" s="4" t="n"/>
-      <c r="B378" s="4" t="n"/>
+      <c r="A378" s="2" t="n"/>
+      <c r="B378" s="2" t="n"/>
+      <c r="C378" s="3" t="n"/>
     </row>
     <row r="379">
-      <c r="A379" s="4" t="n"/>
-      <c r="B379" s="4" t="n"/>
+      <c r="A379" s="2" t="n"/>
+      <c r="B379" s="2" t="n"/>
+      <c r="C379" s="3" t="n"/>
     </row>
     <row r="380">
-      <c r="A380" s="4" t="n"/>
-      <c r="B380" s="4" t="n"/>
+      <c r="A380" s="2" t="n"/>
+      <c r="B380" s="2" t="n"/>
+      <c r="C380" s="3" t="n"/>
     </row>
     <row r="381">
-      <c r="A381" s="4" t="n"/>
-      <c r="B381" s="4" t="n"/>
+      <c r="A381" s="2" t="n"/>
+      <c r="B381" s="2" t="n"/>
+      <c r="C381" s="3" t="n"/>
     </row>
     <row r="382">
-      <c r="A382" s="4" t="n"/>
-      <c r="B382" s="4" t="n"/>
+      <c r="A382" s="2" t="n"/>
+      <c r="B382" s="2" t="n"/>
+      <c r="C382" s="3" t="n"/>
     </row>
     <row r="383">
-      <c r="A383" s="4" t="n"/>
-      <c r="B383" s="4" t="n"/>
+      <c r="A383" s="2" t="n"/>
+      <c r="B383" s="2" t="n"/>
+      <c r="C383" s="3" t="n"/>
     </row>
     <row r="384">
-      <c r="A384" s="4" t="n"/>
-      <c r="B384" s="4" t="n"/>
+      <c r="A384" s="2" t="n"/>
+      <c r="B384" s="2" t="n"/>
+      <c r="C384" s="3" t="n"/>
     </row>
     <row r="385">
-      <c r="A385" s="4" t="n"/>
-      <c r="B385" s="4" t="n"/>
+      <c r="A385" s="2" t="n"/>
+      <c r="B385" s="2" t="n"/>
+      <c r="C385" s="3" t="n"/>
     </row>
     <row r="386">
-      <c r="A386" s="4" t="n"/>
-      <c r="B386" s="4" t="n"/>
+      <c r="A386" s="2" t="n"/>
+      <c r="B386" s="2" t="n"/>
+      <c r="C386" s="3" t="n"/>
     </row>
     <row r="387">
-      <c r="A387" s="4" t="n"/>
-      <c r="B387" s="4" t="n"/>
+      <c r="A387" s="2" t="n"/>
+      <c r="B387" s="2" t="n"/>
+      <c r="C387" s="3" t="n"/>
     </row>
     <row r="388">
-      <c r="A388" s="4" t="n"/>
-      <c r="B388" s="4" t="n"/>
+      <c r="A388" s="2" t="n"/>
+      <c r="B388" s="2" t="n"/>
+      <c r="C388" s="3" t="n"/>
     </row>
     <row r="389">
-      <c r="A389" s="4" t="n"/>
-      <c r="B389" s="4" t="n"/>
+      <c r="A389" s="2" t="n"/>
+      <c r="B389" s="2" t="n"/>
+      <c r="C389" s="3" t="n"/>
     </row>
     <row r="390">
-      <c r="A390" s="4" t="n"/>
-      <c r="B390" s="4" t="n"/>
+      <c r="A390" s="2" t="n"/>
+      <c r="B390" s="2" t="n"/>
+      <c r="C390" s="3" t="n"/>
     </row>
     <row r="391">
-      <c r="A391" s="4" t="n"/>
-      <c r="B391" s="4" t="n"/>
+      <c r="A391" s="2" t="n"/>
+      <c r="B391" s="2" t="n"/>
+      <c r="C391" s="3" t="n"/>
     </row>
     <row r="392">
-      <c r="A392" s="4" t="n"/>
-      <c r="B392" s="4" t="n"/>
+      <c r="A392" s="2" t="n"/>
+      <c r="B392" s="2" t="n"/>
+      <c r="C392" s="3" t="n"/>
     </row>
     <row r="393">
-      <c r="A393" s="4" t="n"/>
-      <c r="B393" s="4" t="n"/>
+      <c r="A393" s="2" t="n"/>
+      <c r="B393" s="2" t="n"/>
+      <c r="C393" s="3" t="n"/>
     </row>
     <row r="394">
-      <c r="A394" s="4" t="n"/>
-      <c r="B394" s="4" t="n"/>
+      <c r="A394" s="2" t="n"/>
+      <c r="B394" s="2" t="n"/>
+      <c r="C394" s="3" t="n"/>
     </row>
     <row r="395">
-      <c r="A395" s="4" t="n"/>
-      <c r="B395" s="4" t="n"/>
+      <c r="A395" s="2" t="n"/>
+      <c r="B395" s="2" t="n"/>
+      <c r="C395" s="3" t="n"/>
     </row>
     <row r="396">
-      <c r="A396" s="4" t="n"/>
-      <c r="B396" s="4" t="n"/>
+      <c r="A396" s="2" t="n"/>
+      <c r="B396" s="2" t="n"/>
+      <c r="C396" s="3" t="n"/>
     </row>
     <row r="397">
-      <c r="A397" s="4" t="n"/>
-      <c r="B397" s="4" t="n"/>
+      <c r="A397" s="2" t="n"/>
+      <c r="B397" s="2" t="n"/>
+      <c r="C397" s="3" t="n"/>
     </row>
     <row r="398">
-      <c r="A398" s="4" t="n"/>
-      <c r="B398" s="4" t="n"/>
+      <c r="A398" s="2" t="n"/>
+      <c r="B398" s="2" t="n"/>
+      <c r="C398" s="3" t="n"/>
     </row>
     <row r="399">
-      <c r="A399" s="4" t="n"/>
-      <c r="B399" s="4" t="n"/>
+      <c r="A399" s="2" t="n"/>
+      <c r="B399" s="2" t="n"/>
+      <c r="C399" s="3" t="n"/>
     </row>
     <row r="400">
-      <c r="A400" s="4" t="n"/>
-      <c r="B400" s="4" t="n"/>
+      <c r="A400" s="2" t="n"/>
+      <c r="B400" s="2" t="n"/>
+      <c r="C400" s="3" t="n"/>
     </row>
     <row r="401">
-      <c r="A401" s="4" t="n"/>
-      <c r="B401" s="4" t="n"/>
+      <c r="A401" s="2" t="n"/>
+      <c r="B401" s="2" t="n"/>
+      <c r="C401" s="3" t="n"/>
     </row>
     <row r="402">
-      <c r="A402" s="4" t="n"/>
-      <c r="B402" s="4" t="n"/>
+      <c r="A402" s="2" t="n"/>
+      <c r="B402" s="2" t="n"/>
+      <c r="C402" s="3" t="n"/>
     </row>
     <row r="403">
-      <c r="A403" s="4" t="n"/>
-      <c r="B403" s="4" t="n"/>
+      <c r="A403" s="2" t="n"/>
+      <c r="B403" s="2" t="n"/>
+      <c r="C403" s="3" t="n"/>
     </row>
     <row r="404">
-      <c r="A404" s="4" t="n"/>
-      <c r="B404" s="4" t="n"/>
+      <c r="A404" s="2" t="n"/>
+      <c r="B404" s="2" t="n"/>
+      <c r="C404" s="3" t="n"/>
     </row>
     <row r="405">
-      <c r="A405" s="4" t="n"/>
-      <c r="B405" s="4" t="n"/>
+      <c r="A405" s="2" t="n"/>
+      <c r="B405" s="2" t="n"/>
+      <c r="C405" s="3" t="n"/>
     </row>
     <row r="406">
-      <c r="A406" s="4" t="n"/>
-      <c r="B406" s="4" t="n"/>
+      <c r="A406" s="2" t="n"/>
+      <c r="B406" s="2" t="n"/>
+      <c r="C406" s="3" t="n"/>
     </row>
     <row r="407">
-      <c r="A407" s="4" t="n"/>
-      <c r="B407" s="4" t="n"/>
+      <c r="A407" s="2" t="n"/>
+      <c r="B407" s="2" t="n"/>
+      <c r="C407" s="3" t="n"/>
     </row>
     <row r="408">
-      <c r="A408" s="4" t="n"/>
-      <c r="B408" s="4" t="n"/>
+      <c r="A408" s="2" t="n"/>
+      <c r="B408" s="2" t="n"/>
+      <c r="C408" s="3" t="n"/>
     </row>
     <row r="409">
-      <c r="A409" s="4" t="n"/>
-      <c r="B409" s="4" t="n"/>
+      <c r="A409" s="2" t="n"/>
+      <c r="B409" s="2" t="n"/>
+      <c r="C409" s="3" t="n"/>
     </row>
     <row r="410">
-      <c r="A410" s="4" t="n"/>
-      <c r="B410" s="4" t="n"/>
+      <c r="A410" s="2" t="n"/>
+      <c r="B410" s="2" t="n"/>
+      <c r="C410" s="3" t="n"/>
     </row>
     <row r="411">
-      <c r="A411" s="4" t="n"/>
-      <c r="B411" s="4" t="n"/>
+      <c r="A411" s="2" t="n"/>
+      <c r="B411" s="2" t="n"/>
+      <c r="C411" s="3" t="n"/>
     </row>
     <row r="412">
-      <c r="A412" s="4" t="n"/>
-      <c r="B412" s="4" t="n"/>
+      <c r="A412" s="2" t="n"/>
+      <c r="B412" s="2" t="n"/>
+      <c r="C412" s="3" t="n"/>
     </row>
     <row r="413">
-      <c r="A413" s="4" t="n"/>
-      <c r="B413" s="4" t="n"/>
+      <c r="A413" s="2" t="n"/>
+      <c r="B413" s="2" t="n"/>
+      <c r="C413" s="3" t="n"/>
     </row>
     <row r="414">
-      <c r="A414" s="4" t="n"/>
-      <c r="B414" s="4" t="n"/>
+      <c r="A414" s="2" t="n"/>
+      <c r="B414" s="2" t="n"/>
+      <c r="C414" s="3" t="n"/>
     </row>
     <row r="415">
-      <c r="A415" s="4" t="n"/>
-      <c r="B415" s="4" t="n"/>
+      <c r="A415" s="2" t="n"/>
+      <c r="B415" s="2" t="n"/>
+      <c r="C415" s="3" t="n"/>
     </row>
     <row r="416">
-      <c r="A416" s="4" t="n"/>
-      <c r="B416" s="4" t="n"/>
+      <c r="A416" s="2" t="n"/>
+      <c r="B416" s="2" t="n"/>
+      <c r="C416" s="3" t="n"/>
     </row>
     <row r="417">
-      <c r="A417" s="4" t="n"/>
-      <c r="B417" s="4" t="n"/>
+      <c r="A417" s="2" t="n"/>
+      <c r="B417" s="2" t="n"/>
+      <c r="C417" s="3" t="n"/>
     </row>
     <row r="418">
-      <c r="A418" s="4" t="n"/>
-      <c r="B418" s="4" t="n"/>
+      <c r="A418" s="2" t="n"/>
+      <c r="B418" s="2" t="n"/>
+      <c r="C418" s="3" t="n"/>
     </row>
     <row r="419">
-      <c r="A419" s="4" t="n"/>
-      <c r="B419" s="4" t="n"/>
+      <c r="A419" s="2" t="n"/>
+      <c r="B419" s="2" t="n"/>
+      <c r="C419" s="3" t="n"/>
     </row>
     <row r="420">
-      <c r="A420" s="4" t="n"/>
-      <c r="B420" s="4" t="n"/>
+      <c r="A420" s="2" t="n"/>
+      <c r="B420" s="2" t="n"/>
+      <c r="C420" s="3" t="n"/>
     </row>
     <row r="421">
-      <c r="A421" s="4" t="n"/>
-      <c r="B421" s="4" t="n"/>
+      <c r="A421" s="2" t="n"/>
+      <c r="B421" s="2" t="n"/>
+      <c r="C421" s="3" t="n"/>
     </row>
     <row r="422">
-      <c r="A422" s="4" t="n"/>
-      <c r="B422" s="4" t="n"/>
+      <c r="A422" s="2" t="n"/>
+      <c r="B422" s="2" t="n"/>
+      <c r="C422" s="3" t="n"/>
     </row>
     <row r="423">
-      <c r="A423" s="4" t="n"/>
-      <c r="B423" s="4" t="n"/>
+      <c r="A423" s="2" t="n"/>
+      <c r="B423" s="2" t="n"/>
+      <c r="C423" s="3" t="n"/>
     </row>
     <row r="424">
-      <c r="A424" s="4" t="n"/>
-      <c r="B424" s="4" t="n"/>
+      <c r="A424" s="2" t="n"/>
+      <c r="B424" s="2" t="n"/>
+      <c r="C424" s="3" t="n"/>
     </row>
     <row r="425">
-      <c r="A425" s="4" t="n"/>
-      <c r="B425" s="4" t="n"/>
+      <c r="A425" s="2" t="n"/>
+      <c r="B425" s="2" t="n"/>
+      <c r="C425" s="3" t="n"/>
     </row>
     <row r="426">
-      <c r="A426" s="4" t="n"/>
-      <c r="B426" s="4" t="n"/>
+      <c r="A426" s="2" t="n"/>
+      <c r="B426" s="2" t="n"/>
+      <c r="C426" s="3" t="n"/>
     </row>
     <row r="427">
-      <c r="A427" s="4" t="n"/>
-      <c r="B427" s="4" t="n"/>
+      <c r="A427" s="2" t="n"/>
+      <c r="B427" s="2" t="n"/>
+      <c r="C427" s="3" t="n"/>
     </row>
     <row r="428">
-      <c r="A428" s="4" t="n"/>
-      <c r="B428" s="4" t="n"/>
+      <c r="A428" s="2" t="n"/>
+      <c r="B428" s="2" t="n"/>
+      <c r="C428" s="3" t="n"/>
     </row>
     <row r="429">
-      <c r="A429" s="4" t="n"/>
-      <c r="B429" s="4" t="n"/>
+      <c r="A429" s="2" t="n"/>
+      <c r="B429" s="2" t="n"/>
+      <c r="C429" s="3" t="n"/>
     </row>
     <row r="430">
-      <c r="A430" s="4" t="n"/>
-      <c r="B430" s="4" t="n"/>
+      <c r="A430" s="2" t="n"/>
+      <c r="B430" s="2" t="n"/>
+      <c r="C430" s="3" t="n"/>
     </row>
     <row r="431">
-      <c r="A431" s="4" t="n"/>
-      <c r="B431" s="4" t="n"/>
+      <c r="A431" s="2" t="n"/>
+      <c r="B431" s="2" t="n"/>
+      <c r="C431" s="3" t="n"/>
     </row>
     <row r="432">
-      <c r="A432" s="4" t="n"/>
-      <c r="B432" s="4" t="n"/>
+      <c r="A432" s="2" t="n"/>
+      <c r="B432" s="2" t="n"/>
+      <c r="C432" s="3" t="n"/>
     </row>
     <row r="433">
-      <c r="A433" s="4" t="n"/>
-      <c r="B433" s="4" t="n"/>
+      <c r="A433" s="2" t="n"/>
+      <c r="B433" s="2" t="n"/>
+      <c r="C433" s="3" t="n"/>
     </row>
     <row r="434">
-      <c r="A434" s="4" t="n"/>
-      <c r="B434" s="4" t="n"/>
+      <c r="A434" s="2" t="n"/>
+      <c r="B434" s="2" t="n"/>
+      <c r="C434" s="3" t="n"/>
     </row>
     <row r="435">
-      <c r="A435" s="4" t="n"/>
-      <c r="B435" s="4" t="n"/>
+      <c r="A435" s="2" t="n"/>
+      <c r="B435" s="2" t="n"/>
+      <c r="C435" s="3" t="n"/>
     </row>
     <row r="436">
-      <c r="A436" s="4" t="n"/>
-      <c r="B436" s="4" t="n"/>
+      <c r="A436" s="2" t="n"/>
+      <c r="B436" s="2" t="n"/>
+      <c r="C436" s="3" t="n"/>
     </row>
     <row r="437">
-      <c r="A437" s="4" t="n"/>
-      <c r="B437" s="4" t="n"/>
+      <c r="A437" s="2" t="n"/>
+      <c r="B437" s="2" t="n"/>
+      <c r="C437" s="3" t="n"/>
     </row>
     <row r="438">
-      <c r="A438" s="4" t="n"/>
-      <c r="B438" s="4" t="n"/>
+      <c r="A438" s="2" t="n"/>
+      <c r="B438" s="2" t="n"/>
+      <c r="C438" s="3" t="n"/>
     </row>
     <row r="439">
-      <c r="A439" s="4" t="n"/>
-      <c r="B439" s="4" t="n"/>
+      <c r="A439" s="2" t="n"/>
+      <c r="B439" s="2" t="n"/>
+      <c r="C439" s="3" t="n"/>
     </row>
     <row r="440">
-      <c r="A440" s="4" t="n"/>
-      <c r="B440" s="4" t="n"/>
+      <c r="A440" s="2" t="n"/>
+      <c r="B440" s="2" t="n"/>
+      <c r="C440" s="3" t="n"/>
     </row>
     <row r="441">
-      <c r="A441" s="4" t="n"/>
-      <c r="B441" s="4" t="n"/>
+      <c r="A441" s="2" t="n"/>
+      <c r="B441" s="2" t="n"/>
+      <c r="C441" s="3" t="n"/>
     </row>
     <row r="442">
-      <c r="A442" s="4" t="n"/>
-      <c r="B442" s="4" t="n"/>
+      <c r="A442" s="2" t="n"/>
+      <c r="B442" s="2" t="n"/>
+      <c r="C442" s="3" t="n"/>
     </row>
     <row r="443">
-      <c r="A443" s="4" t="n"/>
-      <c r="B443" s="4" t="n"/>
+      <c r="A443" s="2" t="n"/>
+      <c r="B443" s="2" t="n"/>
+      <c r="C443" s="3" t="n"/>
     </row>
     <row r="444">
-      <c r="A444" s="4" t="n"/>
-      <c r="B444" s="4" t="n"/>
+      <c r="A444" s="2" t="n"/>
+      <c r="B444" s="2" t="n"/>
+      <c r="C444" s="3" t="n"/>
     </row>
     <row r="445">
-      <c r="A445" s="4" t="n"/>
-      <c r="B445" s="4" t="n"/>
+      <c r="A445" s="2" t="n"/>
+      <c r="B445" s="2" t="n"/>
+      <c r="C445" s="3" t="n"/>
     </row>
     <row r="446">
-      <c r="A446" s="4" t="n"/>
-      <c r="B446" s="4" t="n"/>
+      <c r="A446" s="2" t="n"/>
+      <c r="B446" s="2" t="n"/>
+      <c r="C446" s="3" t="n"/>
     </row>
     <row r="447">
-      <c r="A447" s="4" t="n"/>
-      <c r="B447" s="4" t="n"/>
+      <c r="A447" s="2" t="n"/>
+      <c r="B447" s="2" t="n"/>
+      <c r="C447" s="3" t="n"/>
     </row>
     <row r="448">
-      <c r="A448" s="4" t="n"/>
-      <c r="B448" s="4" t="n"/>
+      <c r="A448" s="2" t="n"/>
+      <c r="B448" s="2" t="n"/>
+      <c r="C448" s="3" t="n"/>
     </row>
     <row r="449">
-      <c r="A449" s="4" t="n"/>
-      <c r="B449" s="4" t="n"/>
+      <c r="A449" s="2" t="n"/>
+      <c r="B449" s="2" t="n"/>
+      <c r="C449" s="3" t="n"/>
     </row>
     <row r="450">
-      <c r="A450" s="4" t="n"/>
-      <c r="B450" s="4" t="n"/>
+      <c r="A450" s="2" t="n"/>
+      <c r="B450" s="2" t="n"/>
+      <c r="C450" s="3" t="n"/>
     </row>
     <row r="451">
-      <c r="A451" s="4" t="n"/>
-      <c r="B451" s="4" t="n"/>
+      <c r="A451" s="2" t="n"/>
+      <c r="B451" s="2" t="n"/>
+      <c r="C451" s="3" t="n"/>
     </row>
     <row r="452">
-      <c r="A452" s="4" t="n"/>
-      <c r="B452" s="4" t="n"/>
+      <c r="A452" s="2" t="n"/>
+      <c r="B452" s="2" t="n"/>
+      <c r="C452" s="3" t="n"/>
     </row>
     <row r="453">
-      <c r="A453" s="4" t="n"/>
-      <c r="B453" s="4" t="n"/>
+      <c r="A453" s="2" t="n"/>
+      <c r="B453" s="2" t="n"/>
+      <c r="C453" s="3" t="n"/>
     </row>
     <row r="454">
-      <c r="A454" s="4" t="n"/>
-      <c r="B454" s="4" t="n"/>
+      <c r="A454" s="2" t="n"/>
+      <c r="B454" s="2" t="n"/>
+      <c r="C454" s="3" t="n"/>
     </row>
     <row r="455">
-      <c r="A455" s="4" t="n"/>
-      <c r="B455" s="4" t="n"/>
+      <c r="A455" s="2" t="n"/>
+      <c r="B455" s="2" t="n"/>
+      <c r="C455" s="3" t="n"/>
     </row>
     <row r="456">
-      <c r="A456" s="4" t="n"/>
-      <c r="B456" s="4" t="n"/>
+      <c r="A456" s="2" t="n"/>
+      <c r="B456" s="2" t="n"/>
+      <c r="C456" s="3" t="n"/>
     </row>
     <row r="457">
-      <c r="A457" s="4" t="n"/>
-      <c r="B457" s="4" t="n"/>
+      <c r="A457" s="2" t="n"/>
+      <c r="B457" s="2" t="n"/>
+      <c r="C457" s="3" t="n"/>
     </row>
     <row r="458">
-      <c r="A458" s="4" t="n"/>
-      <c r="B458" s="4" t="n"/>
+      <c r="A458" s="2" t="n"/>
+      <c r="B458" s="2" t="n"/>
+      <c r="C458" s="3" t="n"/>
     </row>
     <row r="459">
-      <c r="A459" s="4" t="n"/>
-      <c r="B459" s="4" t="n"/>
+      <c r="A459" s="2" t="n"/>
+      <c r="B459" s="2" t="n"/>
+      <c r="C459" s="3" t="n"/>
     </row>
     <row r="460">
-      <c r="A460" s="4" t="n"/>
-      <c r="B460" s="4" t="n"/>
+      <c r="A460" s="2" t="n"/>
+      <c r="B460" s="2" t="n"/>
+      <c r="C460" s="3" t="n"/>
     </row>
     <row r="461">
-      <c r="A461" s="4" t="n"/>
-      <c r="B461" s="4" t="n"/>
+      <c r="A461" s="2" t="n"/>
+      <c r="B461" s="2" t="n"/>
+      <c r="C461" s="3" t="n"/>
     </row>
     <row r="462">
-      <c r="A462" s="4" t="n"/>
-      <c r="B462" s="4" t="n"/>
+      <c r="A462" s="2" t="n"/>
+      <c r="B462" s="2" t="n"/>
+      <c r="C462" s="3" t="n"/>
     </row>
     <row r="463">
-      <c r="A463" s="4" t="n"/>
-      <c r="B463" s="4" t="n"/>
+      <c r="A463" s="2" t="n"/>
+      <c r="B463" s="2" t="n"/>
+      <c r="C463" s="3" t="n"/>
     </row>
     <row r="464">
-      <c r="A464" s="4" t="n"/>
-      <c r="B464" s="4" t="n"/>
+      <c r="A464" s="2" t="n"/>
+      <c r="B464" s="2" t="n"/>
+      <c r="C464" s="3" t="n"/>
     </row>
     <row r="465">
-      <c r="A465" s="4" t="n"/>
-      <c r="B465" s="4" t="n"/>
+      <c r="A465" s="2" t="n"/>
+      <c r="B465" s="2" t="n"/>
+      <c r="C465" s="3" t="n"/>
     </row>
     <row r="466">
-      <c r="A466" s="4" t="n"/>
-      <c r="B466" s="4" t="n"/>
+      <c r="A466" s="2" t="n"/>
+      <c r="B466" s="2" t="n"/>
+      <c r="C466" s="3" t="n"/>
     </row>
     <row r="467">
-      <c r="A467" s="4" t="n"/>
-      <c r="B467" s="4" t="n"/>
+      <c r="A467" s="2" t="n"/>
+      <c r="B467" s="2" t="n"/>
+      <c r="C467" s="3" t="n"/>
     </row>
     <row r="468">
-      <c r="A468" s="4" t="n"/>
-      <c r="B468" s="4" t="n"/>
+      <c r="A468" s="2" t="n"/>
+      <c r="B468" s="2" t="n"/>
+      <c r="C468" s="3" t="n"/>
     </row>
     <row r="469">
-      <c r="A469" s="4" t="n"/>
-      <c r="B469" s="4" t="n"/>
+      <c r="A469" s="2" t="n"/>
+      <c r="B469" s="2" t="n"/>
+      <c r="C469" s="3" t="n"/>
     </row>
     <row r="470">
-      <c r="A470" s="4" t="n"/>
-      <c r="B470" s="4" t="n"/>
+      <c r="A470" s="2" t="n"/>
+      <c r="B470" s="2" t="n"/>
+      <c r="C470" s="3" t="n"/>
     </row>
     <row r="471">
-      <c r="A471" s="4" t="n"/>
-      <c r="B471" s="4" t="n"/>
+      <c r="A471" s="2" t="n"/>
+      <c r="B471" s="2" t="n"/>
+      <c r="C471" s="3" t="n"/>
     </row>
     <row r="472">
-      <c r="A472" s="4" t="n"/>
-      <c r="B472" s="4" t="n"/>
+      <c r="A472" s="2" t="n"/>
+      <c r="B472" s="2" t="n"/>
+      <c r="C472" s="3" t="n"/>
     </row>
     <row r="473">
-      <c r="A473" s="4" t="n"/>
-      <c r="B473" s="4" t="n"/>
+      <c r="A473" s="2" t="n"/>
+      <c r="B473" s="2" t="n"/>
+      <c r="C473" s="3" t="n"/>
     </row>
     <row r="474">
-      <c r="A474" s="4" t="n"/>
-      <c r="B474" s="4" t="n"/>
+      <c r="A474" s="2" t="n"/>
+      <c r="B474" s="2" t="n"/>
+      <c r="C474" s="3" t="n"/>
     </row>
     <row r="475">
-      <c r="A475" s="4" t="n"/>
-      <c r="B475" s="4" t="n"/>
+      <c r="A475" s="2" t="n"/>
+      <c r="B475" s="2" t="n"/>
+      <c r="C475" s="3" t="n"/>
     </row>
     <row r="476">
-      <c r="A476" s="4" t="n"/>
-      <c r="B476" s="4" t="n"/>
+      <c r="A476" s="2" t="n"/>
+      <c r="B476" s="2" t="n"/>
+      <c r="C476" s="3" t="n"/>
     </row>
     <row r="477">
-      <c r="A477" s="4" t="n"/>
-      <c r="B477" s="4" t="n"/>
+      <c r="A477" s="2" t="n"/>
+      <c r="B477" s="2" t="n"/>
+      <c r="C477" s="3" t="n"/>
     </row>
     <row r="478">
-      <c r="A478" s="4" t="n"/>
-      <c r="B478" s="4" t="n"/>
+      <c r="A478" s="2" t="n"/>
+      <c r="B478" s="2" t="n"/>
+      <c r="C478" s="3" t="n"/>
     </row>
     <row r="479">
-      <c r="A479" s="4" t="n"/>
-      <c r="B479" s="4" t="n"/>
+      <c r="A479" s="2" t="n"/>
+      <c r="B479" s="2" t="n"/>
+      <c r="C479" s="3" t="n"/>
     </row>
     <row r="480">
-      <c r="A480" s="4" t="n"/>
-      <c r="B480" s="4" t="n"/>
+      <c r="A480" s="2" t="n"/>
+      <c r="B480" s="2" t="n"/>
+      <c r="C480" s="3" t="n"/>
     </row>
     <row r="481">
-      <c r="A481" s="4" t="n"/>
-      <c r="B481" s="4" t="n"/>
+      <c r="A481" s="2" t="n"/>
+      <c r="B481" s="2" t="n"/>
+      <c r="C481" s="3" t="n"/>
     </row>
     <row r="482">
-      <c r="A482" s="4" t="n"/>
-      <c r="B482" s="4" t="n"/>
+      <c r="A482" s="2" t="n"/>
+      <c r="B482" s="2" t="n"/>
+      <c r="C482" s="3" t="n"/>
     </row>
     <row r="483">
-      <c r="A483" s="4" t="n"/>
-      <c r="B483" s="4" t="n"/>
+      <c r="A483" s="2" t="n"/>
+      <c r="B483" s="2" t="n"/>
+      <c r="C483" s="3" t="n"/>
     </row>
     <row r="484">
-      <c r="A484" s="4" t="n"/>
-      <c r="B484" s="4" t="n"/>
+      <c r="A484" s="2" t="n"/>
+      <c r="B484" s="2" t="n"/>
+      <c r="C484" s="3" t="n"/>
     </row>
     <row r="485">
-      <c r="A485" s="4" t="n"/>
-      <c r="B485" s="4" t="n"/>
+      <c r="A485" s="2" t="n"/>
+      <c r="B485" s="2" t="n"/>
+      <c r="C485" s="3" t="n"/>
     </row>
     <row r="486">
-      <c r="A486" s="4" t="n"/>
-      <c r="B486" s="4" t="n"/>
+      <c r="A486" s="2" t="n"/>
+      <c r="B486" s="2" t="n"/>
+      <c r="C486" s="3" t="n"/>
     </row>
     <row r="487">
-      <c r="A487" s="4" t="n"/>
-      <c r="B487" s="4" t="n"/>
+      <c r="A487" s="2" t="n"/>
+      <c r="B487" s="2" t="n"/>
+      <c r="C487" s="3" t="n"/>
     </row>
     <row r="488">
-      <c r="A488" s="4" t="n"/>
-      <c r="B488" s="4" t="n"/>
+      <c r="A488" s="2" t="n"/>
+      <c r="B488" s="2" t="n"/>
+      <c r="C488" s="3" t="n"/>
     </row>
     <row r="489">
-      <c r="A489" s="4" t="n"/>
-      <c r="B489" s="4" t="n"/>
+      <c r="A489" s="2" t="n"/>
+      <c r="B489" s="2" t="n"/>
+      <c r="C489" s="3" t="n"/>
     </row>
     <row r="490">
-      <c r="A490" s="4" t="n"/>
-      <c r="B490" s="4" t="n"/>
+      <c r="A490" s="2" t="n"/>
+      <c r="B490" s="2" t="n"/>
+      <c r="C490" s="3" t="n"/>
     </row>
     <row r="491">
-      <c r="A491" s="4" t="n"/>
-      <c r="B491" s="4" t="n"/>
+      <c r="A491" s="2" t="n"/>
+      <c r="B491" s="2" t="n"/>
+      <c r="C491" s="3" t="n"/>
     </row>
     <row r="492">
-      <c r="A492" s="4" t="n"/>
-      <c r="B492" s="4" t="n"/>
+      <c r="A492" s="2" t="n"/>
+      <c r="B492" s="2" t="n"/>
+      <c r="C492" s="3" t="n"/>
     </row>
     <row r="493">
-      <c r="A493" s="4" t="n"/>
-      <c r="B493" s="4" t="n"/>
+      <c r="A493" s="2" t="n"/>
+      <c r="B493" s="2" t="n"/>
+      <c r="C493" s="3" t="n"/>
     </row>
     <row r="494">
-      <c r="A494" s="4" t="n"/>
-      <c r="B494" s="4" t="n"/>
+      <c r="A494" s="2" t="n"/>
+      <c r="B494" s="2" t="n"/>
+      <c r="C494" s="3" t="n"/>
     </row>
     <row r="495">
-      <c r="A495" s="4" t="n"/>
-      <c r="B495" s="4" t="n"/>
+      <c r="A495" s="2" t="n"/>
+      <c r="B495" s="2" t="n"/>
+      <c r="C495" s="3" t="n"/>
     </row>
     <row r="496">
-      <c r="A496" s="4" t="n"/>
-      <c r="B496" s="4" t="n"/>
+      <c r="A496" s="2" t="n"/>
+      <c r="B496" s="2" t="n"/>
+      <c r="C496" s="3" t="n"/>
     </row>
     <row r="497">
-      <c r="A497" s="4" t="n"/>
-      <c r="B497" s="4" t="n"/>
+      <c r="A497" s="2" t="n"/>
+      <c r="B497" s="2" t="n"/>
+      <c r="C497" s="3" t="n"/>
     </row>
     <row r="498">
-      <c r="A498" s="4" t="n"/>
-      <c r="B498" s="4" t="n"/>
+      <c r="A498" s="2" t="n"/>
+      <c r="B498" s="2" t="n"/>
+      <c r="C498" s="3" t="n"/>
     </row>
     <row r="499">
-      <c r="A499" s="4" t="n"/>
-      <c r="B499" s="4" t="n"/>
+      <c r="A499" s="2" t="n"/>
+      <c r="B499" s="2" t="n"/>
+      <c r="C499" s="3" t="n"/>
     </row>
     <row r="500">
-      <c r="A500" s="4" t="n"/>
-      <c r="B500" s="4" t="n"/>
+      <c r="A500" s="2" t="n"/>
+      <c r="B500" s="2" t="n"/>
+      <c r="C500" s="3" t="n"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="4" t="n"/>
+      <c r="B501" s="4" t="n"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="4" t="n"/>
+      <c r="B502" s="4" t="n"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="4" t="n"/>
+      <c r="B503" s="4" t="n"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="4" t="n"/>
+      <c r="B504" s="4" t="n"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="4" t="n"/>
+      <c r="B505" s="4" t="n"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="4" t="n"/>
+      <c r="B506" s="4" t="n"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="4" t="n"/>
+      <c r="B507" s="4" t="n"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="4" t="n"/>
+      <c r="B508" s="4" t="n"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="4" t="n"/>
+      <c r="B509" s="4" t="n"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="4" t="n"/>
+      <c r="B510" s="4" t="n"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="4" t="n"/>
+      <c r="B511" s="4" t="n"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="4" t="n"/>
+      <c r="B512" s="4" t="n"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="4" t="n"/>
+      <c r="B513" s="4" t="n"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="4" t="n"/>
+      <c r="B514" s="4" t="n"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="4" t="n"/>
+      <c r="B515" s="4" t="n"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="4" t="n"/>
+      <c r="B516" s="4" t="n"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="4" t="n"/>
+      <c r="B517" s="4" t="n"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="4" t="n"/>
+      <c r="B518" s="4" t="n"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="4" t="n"/>
+      <c r="B519" s="4" t="n"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="4" t="n"/>
+      <c r="B520" s="4" t="n"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="4" t="n"/>
+      <c r="B521" s="4" t="n"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="4" t="n"/>
+      <c r="B522" s="4" t="n"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="4" t="n"/>
+      <c r="B523" s="4" t="n"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="4" t="n"/>
+      <c r="B524" s="4" t="n"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="4" t="n"/>
+      <c r="B525" s="4" t="n"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="4" t="n"/>
+      <c r="B526" s="4" t="n"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="4" t="n"/>
+      <c r="B527" s="4" t="n"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="4" t="n"/>
+      <c r="B528" s="4" t="n"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="4" t="n"/>
+      <c r="B529" s="4" t="n"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="4" t="n"/>
+      <c r="B530" s="4" t="n"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="4" t="n"/>
+      <c r="B531" s="4" t="n"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="4" t="n"/>
+      <c r="B532" s="4" t="n"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="4" t="n"/>
+      <c r="B533" s="4" t="n"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="4" t="n"/>
+      <c r="B534" s="4" t="n"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="4" t="n"/>
+      <c r="B535" s="4" t="n"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="4" t="n"/>
+      <c r="B536" s="4" t="n"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="4" t="n"/>
+      <c r="B537" s="4" t="n"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="4" t="n"/>
+      <c r="B538" s="4" t="n"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="4" t="n"/>
+      <c r="B539" s="4" t="n"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="4" t="n"/>
+      <c r="B540" s="4" t="n"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="4" t="n"/>
+      <c r="B541" s="4" t="n"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="4" t="n"/>
+      <c r="B542" s="4" t="n"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="4" t="n"/>
+      <c r="B543" s="4" t="n"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="4" t="n"/>
+      <c r="B544" s="4" t="n"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="4" t="n"/>
+      <c r="B545" s="4" t="n"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="4" t="n"/>
+      <c r="B546" s="4" t="n"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="4" t="n"/>
+      <c r="B547" s="4" t="n"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="4" t="n"/>
+      <c r="B548" s="4" t="n"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="4" t="n"/>
+      <c r="B549" s="4" t="n"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="4" t="n"/>
+      <c r="B550" s="4" t="n"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="4" t="n"/>
+      <c r="B551" s="4" t="n"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="4" t="n"/>
+      <c r="B552" s="4" t="n"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="4" t="n"/>
+      <c r="B553" s="4" t="n"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="4" t="n"/>
+      <c r="B554" s="4" t="n"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="4" t="n"/>
+      <c r="B555" s="4" t="n"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="4" t="n"/>
+      <c r="B556" s="4" t="n"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="4" t="n"/>
+      <c r="B557" s="4" t="n"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="4" t="n"/>
+      <c r="B558" s="4" t="n"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="4" t="n"/>
+      <c r="B559" s="4" t="n"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="4" t="n"/>
+      <c r="B560" s="4" t="n"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="4" t="n"/>
+      <c r="B561" s="4" t="n"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="4" t="n"/>
+      <c r="B562" s="4" t="n"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="4" t="n"/>
+      <c r="B563" s="4" t="n"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="4" t="n"/>
+      <c r="B564" s="4" t="n"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="4" t="n"/>
+      <c r="B565" s="4" t="n"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="4" t="n"/>
+      <c r="B566" s="4" t="n"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="4" t="n"/>
+      <c r="B567" s="4" t="n"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="4" t="n"/>
+      <c r="B568" s="4" t="n"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="4" t="n"/>
+      <c r="B569" s="4" t="n"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="4" t="n"/>
+      <c r="B570" s="4" t="n"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="4" t="n"/>
+      <c r="B571" s="4" t="n"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="4" t="n"/>
+      <c r="B572" s="4" t="n"/>
+    </row>
+    <row r="573">
+      <c r="A573" s="4" t="n"/>
+      <c r="B573" s="4" t="n"/>
+    </row>
+    <row r="574">
+      <c r="A574" s="4" t="n"/>
+      <c r="B574" s="4" t="n"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="4" t="n"/>
+      <c r="B575" s="4" t="n"/>
+    </row>
+    <row r="576">
+      <c r="A576" s="4" t="n"/>
+      <c r="B576" s="4" t="n"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="4" t="n"/>
+      <c r="B577" s="4" t="n"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="4" t="n"/>
+      <c r="B578" s="4" t="n"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="4" t="n"/>
+      <c r="B579" s="4" t="n"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="4" t="n"/>
+      <c r="B580" s="4" t="n"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="4" t="n"/>
+      <c r="B581" s="4" t="n"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="4" t="n"/>
+      <c r="B582" s="4" t="n"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="4" t="n"/>
+      <c r="B583" s="4" t="n"/>
+    </row>
+    <row r="584">
+      <c r="A584" s="4" t="n"/>
+      <c r="B584" s="4" t="n"/>
+    </row>
+    <row r="585">
+      <c r="A585" s="4" t="n"/>
+      <c r="B585" s="4" t="n"/>
+    </row>
+    <row r="586">
+      <c r="A586" s="4" t="n"/>
+      <c r="B586" s="4" t="n"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="4" t="n"/>
+      <c r="B587" s="4" t="n"/>
+    </row>
+    <row r="588">
+      <c r="A588" s="4" t="n"/>
+      <c r="B588" s="4" t="n"/>
+    </row>
+    <row r="589">
+      <c r="A589" s="4" t="n"/>
+      <c r="B589" s="4" t="n"/>
+    </row>
+    <row r="590">
+      <c r="A590" s="4" t="n"/>
+      <c r="B590" s="4" t="n"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="4" t="n"/>
+      <c r="B591" s="4" t="n"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="4" t="n"/>
+      <c r="B592" s="4" t="n"/>
+    </row>
+    <row r="593">
+      <c r="A593" s="4" t="n"/>
+      <c r="B593" s="4" t="n"/>
+    </row>
+    <row r="594">
+      <c r="A594" s="4" t="n"/>
+      <c r="B594" s="4" t="n"/>
+    </row>
+    <row r="595">
+      <c r="A595" s="4" t="n"/>
+      <c r="B595" s="4" t="n"/>
+    </row>
+    <row r="596">
+      <c r="A596" s="4" t="n"/>
+      <c r="B596" s="4" t="n"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="4" t="n"/>
+      <c r="B597" s="4" t="n"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="4" t="n"/>
+      <c r="B598" s="4" t="n"/>
+    </row>
+    <row r="599">
+      <c r="A599" s="4" t="n"/>
+      <c r="B599" s="4" t="n"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="4" t="n"/>
+      <c r="B600" s="4" t="n"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="4" t="n"/>
+      <c r="B601" s="4" t="n"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="4" t="n"/>
+      <c r="B602" s="4" t="n"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="4" t="n"/>
+      <c r="B603" s="4" t="n"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="4" t="n"/>
+      <c r="B604" s="4" t="n"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="4" t="n"/>
+      <c r="B605" s="4" t="n"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="4" t="n"/>
+      <c r="B606" s="4" t="n"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="4" t="n"/>
+      <c r="B607" s="4" t="n"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="4" t="n"/>
+      <c r="B608" s="4" t="n"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="4" t="n"/>
+      <c r="B609" s="4" t="n"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="4" t="n"/>
+      <c r="B610" s="4" t="n"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="4" t="n"/>
+      <c r="B611" s="4" t="n"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="4" t="n"/>
+      <c r="B612" s="4" t="n"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="4" t="n"/>
+      <c r="B613" s="4" t="n"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="4" t="n"/>
+      <c r="B614" s="4" t="n"/>
+    </row>
+    <row r="615">
+      <c r="A615" s="4" t="n"/>
+      <c r="B615" s="4" t="n"/>
+    </row>
+    <row r="616">
+      <c r="A616" s="4" t="n"/>
+      <c r="B616" s="4" t="n"/>
+    </row>
+    <row r="617">
+      <c r="A617" s="4" t="n"/>
+      <c r="B617" s="4" t="n"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="4" t="n"/>
+      <c r="B618" s="4" t="n"/>
+    </row>
+    <row r="619">
+      <c r="A619" s="4" t="n"/>
+      <c r="B619" s="4" t="n"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="4" t="n"/>
+      <c r="B620" s="4" t="n"/>
+    </row>
+    <row r="621">
+      <c r="A621" s="4" t="n"/>
+      <c r="B621" s="4" t="n"/>
+    </row>
+    <row r="622">
+      <c r="A622" s="4" t="n"/>
+      <c r="B622" s="4" t="n"/>
+    </row>
+    <row r="623">
+      <c r="A623" s="4" t="n"/>
+      <c r="B623" s="4" t="n"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="4" t="n"/>
+      <c r="B624" s="4" t="n"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="4" t="n"/>
+      <c r="B625" s="4" t="n"/>
+    </row>
+    <row r="626">
+      <c r="A626" s="4" t="n"/>
+      <c r="B626" s="4" t="n"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="4" t="n"/>
+      <c r="B627" s="4" t="n"/>
+    </row>
+    <row r="628">
+      <c r="A628" s="4" t="n"/>
+      <c r="B628" s="4" t="n"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="4" t="n"/>
+      <c r="B629" s="4" t="n"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="4" t="n"/>
+      <c r="B630" s="4" t="n"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="4" t="n"/>
+      <c r="B631" s="4" t="n"/>
+    </row>
+    <row r="632">
+      <c r="A632" s="4" t="n"/>
+      <c r="B632" s="4" t="n"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="4" t="n"/>
+      <c r="B633" s="4" t="n"/>
+    </row>
+    <row r="634">
+      <c r="A634" s="4" t="n"/>
+      <c r="B634" s="4" t="n"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="4" t="n"/>
+      <c r="B635" s="4" t="n"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="4" t="n"/>
+      <c r="B636" s="4" t="n"/>
+    </row>
+    <row r="637">
+      <c r="A637" s="4" t="n"/>
+      <c r="B637" s="4" t="n"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="4" t="n"/>
+      <c r="B638" s="4" t="n"/>
+    </row>
+    <row r="639">
+      <c r="A639" s="4" t="n"/>
+      <c r="B639" s="4" t="n"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="4" t="n"/>
+      <c r="B640" s="4" t="n"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="4" t="n"/>
+      <c r="B641" s="4" t="n"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="4" t="n"/>
+      <c r="B642" s="4" t="n"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="4" t="n"/>
+      <c r="B643" s="4" t="n"/>
+    </row>
+    <row r="644">
+      <c r="A644" s="4" t="n"/>
+      <c r="B644" s="4" t="n"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="4" t="n"/>
+      <c r="B645" s="4" t="n"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="4" t="n"/>
+      <c r="B646" s="4" t="n"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="4" t="n"/>
+      <c r="B647" s="4" t="n"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="4" t="n"/>
+      <c r="B648" s="4" t="n"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="4" t="n"/>
+      <c r="B649" s="4" t="n"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="4" t="n"/>
+      <c r="B650" s="4" t="n"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="4" t="n"/>
+      <c r="B651" s="4" t="n"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="4" t="n"/>
+      <c r="B652" s="4" t="n"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="4" t="n"/>
+      <c r="B653" s="4" t="n"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="4" t="n"/>
+      <c r="B654" s="4" t="n"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="4" t="n"/>
+      <c r="B655" s="4" t="n"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="4" t="n"/>
+      <c r="B656" s="4" t="n"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="4" t="n"/>
+      <c r="B657" s="4" t="n"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="4" t="n"/>
+      <c r="B658" s="4" t="n"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="4" t="n"/>
+      <c r="B659" s="4" t="n"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="4" t="n"/>
+      <c r="B660" s="4" t="n"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="4" t="n"/>
+      <c r="B661" s="4" t="n"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="4" t="n"/>
+      <c r="B662" s="4" t="n"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="4" t="n"/>
+      <c r="B663" s="4" t="n"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="4" t="n"/>
+      <c r="B664" s="4" t="n"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="4" t="n"/>
+      <c r="B665" s="4" t="n"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="4" t="n"/>
+      <c r="B666" s="4" t="n"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="4" t="n"/>
+      <c r="B667" s="4" t="n"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="4" t="n"/>
+      <c r="B668" s="4" t="n"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="4" t="n"/>
+      <c r="B669" s="4" t="n"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="4" t="n"/>
+      <c r="B670" s="4" t="n"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="4" t="n"/>
+      <c r="B671" s="4" t="n"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="4" t="n"/>
+      <c r="B672" s="4" t="n"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="4" t="n"/>
+      <c r="B673" s="4" t="n"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="4" t="n"/>
+      <c r="B674" s="4" t="n"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="4" t="n"/>
+      <c r="B675" s="4" t="n"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="4" t="n"/>
+      <c r="B676" s="4" t="n"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="4" t="n"/>
+      <c r="B677" s="4" t="n"/>
+    </row>
+    <row r="678">
+      <c r="A678" s="4" t="n"/>
+      <c r="B678" s="4" t="n"/>
+    </row>
+    <row r="679">
+      <c r="A679" s="4" t="n"/>
+      <c r="B679" s="4" t="n"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="4" t="n"/>
+      <c r="B680" s="4" t="n"/>
+    </row>
+    <row r="681">
+      <c r="A681" s="4" t="n"/>
+      <c r="B681" s="4" t="n"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="4" t="n"/>
+      <c r="B682" s="4" t="n"/>
+    </row>
+    <row r="683">
+      <c r="A683" s="4" t="n"/>
+      <c r="B683" s="4" t="n"/>
+    </row>
+    <row r="684">
+      <c r="A684" s="4" t="n"/>
+      <c r="B684" s="4" t="n"/>
+    </row>
+    <row r="685">
+      <c r="A685" s="4" t="n"/>
+      <c r="B685" s="4" t="n"/>
+    </row>
+    <row r="686">
+      <c r="A686" s="4" t="n"/>
+      <c r="B686" s="4" t="n"/>
+    </row>
+    <row r="687">
+      <c r="A687" s="4" t="n"/>
+      <c r="B687" s="4" t="n"/>
+    </row>
+    <row r="688">
+      <c r="A688" s="4" t="n"/>
+      <c r="B688" s="4" t="n"/>
+    </row>
+    <row r="689">
+      <c r="A689" s="4" t="n"/>
+      <c r="B689" s="4" t="n"/>
+    </row>
+    <row r="690">
+      <c r="A690" s="4" t="n"/>
+      <c r="B690" s="4" t="n"/>
+    </row>
+    <row r="691">
+      <c r="A691" s="4" t="n"/>
+      <c r="B691" s="4" t="n"/>
+    </row>
+    <row r="692">
+      <c r="A692" s="4" t="n"/>
+      <c r="B692" s="4" t="n"/>
+    </row>
+    <row r="693">
+      <c r="A693" s="4" t="n"/>
+      <c r="B693" s="4" t="n"/>
+    </row>
+    <row r="694">
+      <c r="A694" s="4" t="n"/>
+      <c r="B694" s="4" t="n"/>
+    </row>
+    <row r="695">
+      <c r="A695" s="4" t="n"/>
+      <c r="B695" s="4" t="n"/>
+    </row>
+    <row r="696">
+      <c r="A696" s="4" t="n"/>
+      <c r="B696" s="4" t="n"/>
+    </row>
+    <row r="697">
+      <c r="A697" s="4" t="n"/>
+      <c r="B697" s="4" t="n"/>
+    </row>
+    <row r="698">
+      <c r="A698" s="4" t="n"/>
+      <c r="B698" s="4" t="n"/>
+    </row>
+    <row r="699">
+      <c r="A699" s="4" t="n"/>
+      <c r="B699" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"自制,外协"</formula1>
     </dataValidation>
   </dataValidations>
